--- a/TABLEAU_DE_BORD_EXPLOITATION.xlsx
+++ b/TABLEAU_DE_BORD_EXPLOITATION.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HPPROB~1\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9486D6CD-CBFE-467D-87EA-593A2517DD59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{49C7293E-F9C8-4961-8178-DE0E4FFFFFE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2472" yWindow="2472" windowWidth="17280" windowHeight="8880" xr2:uid="{1BBFD0E4-420E-4314-8A1E-CC725BC934C0}"/>
+    <workbookView xWindow="2472" yWindow="2472" windowWidth="17280" windowHeight="8880" xr2:uid="{9F4751C8-6260-474C-A39A-B9631EA72652}"/>
   </bookViews>
   <sheets>
     <sheet name="Vue d'ensemble" sheetId="1" r:id="rId1"/>
@@ -19,9 +19,10 @@
     <sheet name="Catalogue modules Tier1" sheetId="4" r:id="rId4"/>
     <sheet name="Operations Control-M" sheetId="5" r:id="rId5"/>
     <sheet name="Reference complete jobs" sheetId="6" r:id="rId6"/>
-    <sheet name="Illustrations CLIM AUTO COUL" sheetId="7" r:id="rId7"/>
-    <sheet name="Vocabulaire et Control-M" sheetId="8" r:id="rId8"/>
-    <sheet name="Securite et notifications" sheetId="9" r:id="rId9"/>
+    <sheet name="Illustrations 3 entreprises" sheetId="7" r:id="rId7"/>
+    <sheet name="Avantages licence Enterprise" sheetId="8" r:id="rId8"/>
+    <sheet name="Vocabulaire et Control-M" sheetId="9" r:id="rId9"/>
+    <sheet name="Securite et notifications" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1156" uniqueCount="796">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1265" uniqueCount="889">
   <si>
     <t>ERP_CRM_FACTORY - Tableau de bord d'exploitation</t>
   </si>
@@ -77,7 +78,7 @@
     <t>Meme orchestrateur bash que WAZ_ELK_FACTORY (jobs_table.csv, IN_COND/OUT_COND) - reutilise tel quel, projet volontairement autonome</t>
   </si>
   <si>
-    <t>ETAT REEL AU 2026-09-01</t>
+    <t>ETAT REEL AU 2026-09-01 (soir)</t>
   </si>
   <si>
     <t>(verifie en base a chaque etape, jamais suppose - voir docs/JOURNAL_TECHNIQUE.md)</t>
@@ -98,7 +99,7 @@
     <t>Tier 2</t>
   </si>
   <si>
-    <t>10 jobs - illustrations personnalisees CLIM AUTO / COUL (RH + CRM), verifiees en base</t>
+    <t>16 jobs - illustrations personnalisees CLIM AUTO / COUL / PAIN &amp; GLACE (RH + CRM + Stock + Factures envoyees par email), verifiees en base</t>
   </si>
   <si>
     <t>Notifications</t>
@@ -107,6 +108,18 @@
     <t>Alertes email reelles actives (contact@ankrr.fr), testees de bout en bout</t>
   </si>
   <si>
+    <t>Email sortant Odoo</t>
+  </si>
+  <si>
+    <t>Configure sur le vrai relais OVH - voir feuille Securite pour l'incident reel et sa correction</t>
+  </si>
+  <si>
+    <t>REGLE D'OR POUR LE PILOTE</t>
+  </si>
+  <si>
+    <t>Chaque job de ce classeur qui touche Odoo passe par le VRAI moteur Odoo (ORM, meme code qu'un clic reel dans l'interface web) - ce qui se joue en CLI se voit IMMEDIATEMENT dans l'interface web (https://erp.odoo.local/), jamais une simulation separee.</t>
+  </si>
+  <si>
     <t>Structure de ce classeur</t>
   </si>
   <si>
@@ -125,7 +138,7 @@
     <t>procedure complete (avec/sans compte)</t>
   </si>
   <si>
-    <t>Catalogue modules Tier 1</t>
+    <t>Catalogue modules Tier1</t>
   </si>
   <si>
     <t>les 34 modules Community reels, verifies en base</t>
@@ -140,13 +153,19 @@
     <t>Reference complete des jobs</t>
   </si>
   <si>
-    <t>les 98 jobs du projet, un par ligne</t>
-  </si>
-  <si>
-    <t>Illustrations CLIM AUTO COUL</t>
-  </si>
-  <si>
-    <t>le detail des donnees de demo construites</t>
+    <t>tous les jobs du projet, un par ligne, generes depuis jobs_table.csv</t>
+  </si>
+  <si>
+    <t>Illustrations 3 entreprises</t>
+  </si>
+  <si>
+    <t>CLIM AUTO, COUL, PAIN &amp; GLACE - RH, CRM, stock, factures envoyees par email</t>
+  </si>
+  <si>
+    <t>Avantages licence Enterprise</t>
+  </si>
+  <si>
+    <t>argumentaire reel, module par module, pour le prospect PAIN &amp; GLACE</t>
   </si>
   <si>
     <t>Vocabulaire et Control-M</t>
@@ -158,7 +177,7 @@
     <t>Securite et notifications</t>
   </si>
   <si>
-    <t>secrets, alertes email, lecons reelles</t>
+    <t>secrets, alertes email, incidents reels et corrections</t>
   </si>
   <si>
     <t>1. cd ~</t>
@@ -176,13 +195,19 @@
     <t>5. Ajuster vars.conf : FACTORY_HOST_IP, mots de passe VM (jamais en dur, via secrets/)</t>
   </si>
   <si>
-    <t>6. ./orchestrator.sh   (installe tout le Tier 0 - environ 25-30 minutes, dont ~7 min de compilation Python 3.11)</t>
-  </si>
-  <si>
-    <t>7. Activer un module a la demande : ./executer_maintenant.sh MOD_CRM_ACTIVATE</t>
-  </si>
-  <si>
-    <t>8. Voir le statut a tout moment : ./statut_live.sh</t>
+    <t>6. Deposer le mot de passe SMTP : echo -n 'mot_de_passe' &gt; ~/erp_crm_factory/secrets/smtp_password.txt &amp;&amp; chmod 600 ~/erp_crm_factory/secrets/smtp_password.txt</t>
+  </si>
+  <si>
+    <t>7. ./orchestrator.sh   (installe tout le Tier 0 - environ 25-30 minutes, dont ~7 min de compilation Python 3.11)</t>
+  </si>
+  <si>
+    <t>8. Activer un module a la demande : ./executer_maintenant.sh MOD_CRM_ACTIVATE</t>
+  </si>
+  <si>
+    <t>9. Rejouer une illustration a la demande : ./executer_maintenant.sh ILL_CLIMAUTO_FACTURE_MAIL</t>
+  </si>
+  <si>
+    <t>10. Voir le statut a tout moment : ./statut_live.sh</t>
   </si>
   <si>
     <t>Destination du clone toujours identique : ~/erp_crm_factory (le 'cd ~' initial est volontaire - jamais un chemin qui depend du repertoire de depart).</t>
@@ -212,7 +237,7 @@
     <t>git status   (doit afficher 'nothing to commit, working tree clean' - ne jamais continuer sur un clone partiel)</t>
   </si>
   <si>
-    <t>find . -name '*.sh' | wc -l   (doit approcher le nombre reel de scripts du depot)</t>
+    <t>find . -name '*.sh' | wc -l</t>
   </si>
   <si>
     <t>chmod +x orchestrator.sh jobs/*.sh *.sh</t>
@@ -233,7 +258,7 @@
     <t>cd ECF-main</t>
   </si>
   <si>
-    <t>C. Optionnel - compte GitHub personnel (fork/versionner ses propres modifications)</t>
+    <t>C. Optionnel - compte GitHub personnel</t>
   </si>
   <si>
     <t>1. https://github.com/signup</t>
@@ -308,7 +333,7 @@
     <t>mail</t>
   </si>
   <si>
-    <t>Messagerie interne - RESTE ACTIF EN PERMANENCE (infrastructure, voir feuille Securite)</t>
+    <t>Messagerie interne - RESTE ACTIF EN PERMANENCE (infrastructure)</t>
   </si>
   <si>
     <t>MOD_DISCUSS_ACTIVATE</t>
@@ -323,7 +348,7 @@
     <t>crm</t>
   </si>
   <si>
-    <t>Suivi des pistes et opportunites - RESTE ACTIF (porte les donnees CLIM AUTO/COUL)</t>
+    <t>Suivi des pistes et opportunites - RESTE ACTIF (porte CLIM AUTO/COUL)</t>
   </si>
   <si>
     <t>MOD_CRM_ACTIVATE</t>
@@ -353,7 +378,7 @@
     <t>account</t>
   </si>
   <si>
-    <t>Facturation et comptabilite de base</t>
+    <t>Facturation et comptabilite - RESTE ACTIF (porte les factures reelles)</t>
   </si>
   <si>
     <t>MOD_COMPTA_ACTIVATE</t>
@@ -383,7 +408,7 @@
     <t>stock</t>
   </si>
   <si>
-    <t>Gestion des stocks et logistique</t>
+    <t>Gestion des stocks - RESTE ACTIF (porte le stock PAIN &amp; GLACE)</t>
   </si>
   <si>
     <t>MOD_STOCK_ACTIVATE</t>
@@ -548,7 +573,7 @@
     <t>hr</t>
   </si>
   <si>
-    <t>Fiches employes - RESTE ACTIF (porte les equipes CLIM AUTO/COUL)</t>
+    <t>Fiches employes - RESTE ACTIF (porte les equipes des 3 entreprises)</t>
   </si>
   <si>
     <t>MOD_RH_ACTIVATE</t>
@@ -578,7 +603,7 @@
     <t>hr_holidays</t>
   </si>
   <si>
-    <t>Demandes de conges - RESTE ACTIF (porte une illustration)</t>
+    <t>Demandes de conges - RESTE ACTIF</t>
   </si>
   <si>
     <t>MOD_CONGES_ACTIVATE</t>
@@ -608,7 +633,7 @@
     <t>hr_recruitment</t>
   </si>
   <si>
-    <t>Pipeline de recrutement - RESTE ACTIF (porte une illustration)</t>
+    <t>Pipeline de recrutement - RESTE ACTIF</t>
   </si>
   <si>
     <t>MOD_RECRUTEMENT_ACTIVATE</t>
@@ -782,7 +807,7 @@
     <t>MOD_RECYCLAGE_DEACTIVATE</t>
   </si>
   <si>
-    <t>20 modules Enterprise (payants, verifies 'uninstallable' sur ce serveur Community) volontairement exclus : accountant, appointment, helpdesk, hr_appraisal, industry_fsm, knowledge, marketing_automation, mrp_plm, mrp_workorder, planning, quality_control, sale_amazon, sale_subscription, sign, social, stock_barcode, timesheet_grid, voip, web_mobile, web_studio.</t>
+    <t>20 modules Enterprise (payants, verifies 'uninstallable' sur ce serveur Community) exclus de ce catalogue - voir feuille 'Avantages licence Enterprise' pour leur valeur reelle.</t>
   </si>
   <si>
     <t>Les 13 operations d'exploitation, faÃ§on BMC Control-M</t>
@@ -800,7 +825,7 @@
     <t>Rerun</t>
   </si>
   <si>
-    <t>Relance une NOUVELLE instance d'un job deja execute (efface sa condition de sortie), respecte toujours ses dependances reelles</t>
+    <t>Relance une NOUVELLE instance d'un job deja execute, respecte toujours ses dependances reelles</t>
   </si>
   <si>
     <t>./rejouer_job.sh &lt;JOB_ID&gt; "&lt;raison&gt;"</t>
@@ -809,7 +834,7 @@
     <t>Force Run</t>
   </si>
   <si>
-    <t>Lance un job MEME SI ses dependances ne sont pas satisfaites (avec avertissement, jamais silencieux)</t>
+    <t>Lance un job MEME SI ses dependances ne sont pas satisfaites</t>
   </si>
   <si>
     <t>./forcer_job.sh &lt;JOB_ID&gt; "&lt;raison&gt;"</t>
@@ -818,7 +843,7 @@
     <t>Bypass / Set to OK</t>
   </si>
   <si>
-    <t>Marque un job comme deja reussi SANS l'executer, libere ce qui en depend</t>
+    <t>Marque un job comme deja reussi SANS l'executer</t>
   </si>
   <si>
     <t>./marquer_deja_fait.sh &lt;JOB_ID&gt; "&lt;raison&gt;"</t>
@@ -827,7 +852,7 @@
     <t>Run Now</t>
   </si>
   <si>
-    <t>Lance immediatement un job DEJA pret (dependances satisfaites), sans attendre le prochain passage complet</t>
+    <t>Lance immediatement un job DEJA pret</t>
   </si>
   <si>
     <t>./executer_maintenant.sh &lt;JOB_ID&gt;</t>
@@ -836,7 +861,7 @@
     <t>Hold</t>
   </si>
   <si>
-    <t>Bloque un job en memoire, meme si ses dependances sont remplies</t>
+    <t>Bloque un job en memoire, meme pret</t>
   </si>
   <si>
     <t>./geler_job.sh &lt;JOB_ID&gt; "&lt;raison&gt;"</t>
@@ -845,7 +870,7 @@
     <t>Release</t>
   </si>
   <si>
-    <t>Debloque un job precedemment gele (Hold)</t>
+    <t>Debloque un job precedemment gele</t>
   </si>
   <si>
     <t>./liberer_job.sh &lt;JOB_ID&gt;</t>
@@ -854,16 +879,16 @@
     <t>Kill / Terminate</t>
   </si>
   <si>
-    <t>Envoie SIGTERM puis SIGKILL (si besoin) a un job EN COURS d'execution</t>
+    <t>SIGTERM puis SIGKILL sur un job EN COURS</t>
   </si>
   <si>
     <t>./tuer_job.sh &lt;JOB_ID&gt; "&lt;raison&gt;"</t>
   </si>
   <si>
-    <t>Confirm (pose l'exigence)</t>
-  </si>
-  <si>
-    <t>Exige une approbation manuelle avant la prochaine execution d'un job sensible</t>
+    <t>Confirm (pose)</t>
+  </si>
+  <si>
+    <t>Exige une approbation manuelle avant la prochaine execution</t>
   </si>
   <si>
     <t>./exiger_confirmation.sh &lt;JOB_ID&gt; "&lt;raison&gt;"</t>
@@ -872,7 +897,7 @@
     <t>Confirm (approuve)</t>
   </si>
   <si>
-    <t>Leve l'exigence de confirmation et lance le job si pret</t>
+    <t>Leve l'exigence et lance si pret</t>
   </si>
   <si>
     <t>./confirmer_job.sh &lt;JOB_ID&gt; "&lt;raison&gt;"</t>
@@ -881,7 +906,7 @@
     <t>Delete</t>
   </si>
   <si>
-    <t>Retire un job du plan d'execution courant (invisible pour statut_live.sh)</t>
+    <t>Retire un job du plan d'execution courant</t>
   </si>
   <si>
     <t>./supprimer_job.sh &lt;JOB_ID&gt; "&lt;raison&gt;"</t>
@@ -899,7 +924,7 @@
     <t>View Output / Sysout</t>
   </si>
   <si>
-    <t>Affiche la sortie reelle d'une execution precise d'un job</t>
+    <t>Sortie reelle d'une execution precise</t>
   </si>
   <si>
     <t>./historique_job.sh &lt;JOB_ID&gt; &lt;numero&gt;</t>
@@ -908,13 +933,13 @@
     <t>View Log / View History</t>
   </si>
   <si>
-    <t>Liste toutes les executions passees d'un job, avec statistiques</t>
-  </si>
-  <si>
-    <t>./historique_job.sh &lt;JOB_ID&gt;   ou   ./historique_job.sh &lt;JOB_ID&gt; stats</t>
-  </si>
-  <si>
-    <t>Chaque action exige une raison et retape le JOB_ID en confirmation (discipline d'audit) - aucune derogation manuelle silencieuse dans ce projet.</t>
+    <t>Toutes les executions passees, avec statistiques</t>
+  </si>
+  <si>
+    <t>./historique_job.sh &lt;JOB_ID&gt;   ou   stats</t>
+  </si>
+  <si>
+    <t>Chaque action exige une raison et retape le JOB_ID en confirmation (discipline d'audit) - aucune derogation manuelle silencieuse.</t>
   </si>
   <si>
     <t>Reference complete des jobs (source : jobs_table.csv, generee automatiquement)</t>
@@ -2237,67 +2262,307 @@
     <t>ODOO_SMTP_TEST_OK</t>
   </si>
   <si>
-    <t>Illustrations personnalisees - CLIM AUTO et COUL</t>
+    <t>ODOO_MAIL_SERVER_REAL</t>
+  </si>
+  <si>
+    <t>ECF_SYS_RUN_MAILSERVERREAL</t>
+  </si>
+  <si>
+    <t>ODOO_MAIL_SERVER_REAL.sh</t>
+  </si>
+  <si>
+    <t>Configure Odoo pour envoyer ses emails reels via contact@ankrr.fr</t>
+  </si>
+  <si>
+    <t>ODOO_MAIL_SERVER_REAL_OK</t>
+  </si>
+  <si>
+    <t>ILL_CLIMAUTO_FACTURE_MAIL</t>
+  </si>
+  <si>
+    <t>ECF_CLIMAUTO_RUN_FACTUREMAIL</t>
+  </si>
+  <si>
+    <t>ILL_CLIMAUTO_FACTURE_MAIL.sh</t>
+  </si>
+  <si>
+    <t>Illustration : facture CLIM AUTO reelle envoyee par email</t>
+  </si>
+  <si>
+    <t>ODOO_MAIL_SERVER_REAL_OK|COMPTA_ACTIVE|ILL_CLIMAUTO_SOCIETE_OK</t>
+  </si>
+  <si>
+    <t>ILL_CLIMAUTO_FACTURE_OK</t>
+  </si>
+  <si>
+    <t>ILL_COUL_FACTURE_MAIL</t>
+  </si>
+  <si>
+    <t>ECF_COUL_RUN_FACTUREMAIL</t>
+  </si>
+  <si>
+    <t>ILL_COUL_FACTURE_MAIL.sh</t>
+  </si>
+  <si>
+    <t>Illustration : facture COUL reelle envoyee par email</t>
+  </si>
+  <si>
+    <t>ODOO_MAIL_SERVER_REAL_OK|COMPTA_ACTIVE|ILL_COUL_SOCIETE_OK</t>
+  </si>
+  <si>
+    <t>ILL_COUL_FACTURE_OK</t>
+  </si>
+  <si>
+    <t>ILL_BOULANGERIE_SOCIETE</t>
+  </si>
+  <si>
+    <t>ECF_BOULANGERIE_RUN_SOCIETE</t>
+  </si>
+  <si>
+    <t>ILL_BOULANGERIE_SOCIETE.sh</t>
+  </si>
+  <si>
+    <t>Illustration : creation de la societe PAIN &amp; GLACE (boulangerie-glacier Yopougon)</t>
+  </si>
+  <si>
+    <t>ILL_BOULANGERIE_SOCIETE_OK</t>
+  </si>
+  <si>
+    <t>ILL_BOULANGERIE_STOCK</t>
+  </si>
+  <si>
+    <t>ECF_BOULANGERIE_RUN_STOCK</t>
+  </si>
+  <si>
+    <t>ILL_BOULANGERIE_STOCK.sh</t>
+  </si>
+  <si>
+    <t>Illustration : produits et stock initial PAIN &amp; GLACE (remplace le suivi Excel)</t>
+  </si>
+  <si>
+    <t>STOCK_ACTIVE|ILL_BOULANGERIE_SOCIETE_OK</t>
+  </si>
+  <si>
+    <t>ILL_BOULANGERIE_STOCK_OK</t>
+  </si>
+  <si>
+    <t>ILL_BOULANGERIE_FACTURE_MAIL</t>
+  </si>
+  <si>
+    <t>ECF_BOULANGERIE_RUN_FACTUREMAIL</t>
+  </si>
+  <si>
+    <t>ILL_BOULANGERIE_FACTURE_MAIL.sh</t>
+  </si>
+  <si>
+    <t>Illustration : facture PAIN &amp; GLACE reelle envoyee par email</t>
+  </si>
+  <si>
+    <t>ODOO_MAIL_SERVER_REAL_OK|COMPTA_ACTIVE|ILL_BOULANGERIE_STOCK_OK</t>
+  </si>
+  <si>
+    <t>ILL_BOULANGERIE_FACTURE_OK</t>
+  </si>
+  <si>
+    <t>Illustrations personnalisees - CLIM AUTO, COUL, PAIN &amp; GLACE</t>
   </si>
   <si>
     <t>CLIM AUTO</t>
   </si>
   <si>
-    <t>Garage / atelier climatisation automobile, Cocody, Abidjan - contact@climauto.ci</t>
-  </si>
-  <si>
-    <t>Societe (Odoo)</t>
-  </si>
-  <si>
-    <t>res.company reelle - job ILL_CLIMAUTO_SOCIETE</t>
+    <t>Garage / atelier climatisation automobile, Cocody, Abidjan</t>
+  </si>
+  <si>
+    <t>Societe</t>
+  </si>
+  <si>
+    <t>res.company reelle - ILL_CLIMAUTO_SOCIETE</t>
   </si>
   <si>
     <t>Equipe RH (5)</t>
   </si>
   <si>
-    <t>Kouadio Yao Bertin (chef d'atelier), Traore Aminata (accueil), N'Guessan Serge (mecanicien clim), Kone Fatoumata (comptabilite), Bamba Souleymane (mecanicien polyvalent) - job ILL_CLIMAUTO_EMPLOYES</t>
+    <t>Chef d'atelier, accueil, 2 mecaniciens, comptabilite - ILL_CLIMAUTO_EMPLOYES</t>
   </si>
   <si>
     <t>Pipeline CRM (4)</t>
   </si>
   <si>
-    <t>Revision clim Toyota Hilux, diagnostic panne Hyundai Tucson, contrat entretien flotte 8 vehicules, recharge gaz Peugeot 308 (gagnee) - job ILL_CLIMAUTO_CRM_PISTES</t>
-  </si>
-  <si>
-    <t>Conges</t>
-  </si>
-  <si>
-    <t>1 demande (Traore Aminata, type Unpaid) - job ILL_CLIMAUTO_CONGES</t>
-  </si>
-  <si>
-    <t>Recrutement</t>
-  </si>
-  <si>
-    <t>Offre 'Mecanicien climatisation auto' + candidat Diaby Moussa - job ILL_CLIMAUTO_RECRUTEMENT</t>
+    <t>Revision Toyota Hilux, diagnostic Hyundai Tucson, contrat flotte 8 vehicules, recharge gaz (gagnee) - ILL_CLIMAUTO_CRM_PISTES</t>
+  </si>
+  <si>
+    <t>Conges + Recrutement</t>
+  </si>
+  <si>
+    <t>1 demande de conges, 1 offre + candidat mecanicien - ILL_CLIMAUTO_CONGES / ILL_CLIMAUTO_RECRUTEMENT</t>
+  </si>
+  <si>
+    <t>Facture reelle envoyee par email</t>
+  </si>
+  <si>
+    <t>Revision + compresseur + gaz + main d'oeuvre (285 000 F CFA), postee et envoyee a contact@ankrr.fr - ILL_CLIMAUTO_FACTURE_MAIL</t>
   </si>
   <si>
     <t>COUL</t>
   </si>
   <si>
-    <t>Parfumerie, Le Plateau, Abidjan - contact@coul.ci</t>
-  </si>
-  <si>
-    <t>res.company reelle - job ILL_COUL_SOCIETE</t>
+    <t>Parfumerie, Le Plateau, Abidjan</t>
+  </si>
+  <si>
+    <t>res.company reelle - ILL_COUL_SOCIETE</t>
   </si>
   <si>
     <t>Equipe RH (4)</t>
   </si>
   <si>
-    <t>Diomande Marie-Claire (responsable boutique), Yao Prisca (conseillere vente), Ouattara Ibrahim (stock), Konan Grace (comptabilite) - job ILL_COUL_EMPLOYES</t>
-  </si>
-  <si>
-    <t>Commande grossiste 200 flacons, ouverture compte pro salon de coiffure, coffret cadeau entreprise, vente parfum homme (gagnee) - job ILL_COUL_CRM_PISTES</t>
-  </si>
-  <si>
-    <t>REGLE IMPORTANTE</t>
-  </si>
-  <si>
-    <t>Desinstaller un module Odoo supprime REELLEMENT ses tables SQL (verifie : hr_employee/crm_lead disparaissent completement) - RH et CRM restent donc actifs en PERMANENCE pour ne jamais perdre ce travail. Pour la demo, la mise en scene 'j'active le module devant le client' ne s'applique qu'aux modules SANS donnees d'illustration.</t>
+    <t>Responsable boutique, conseillere vente, stock, comptabilite - ILL_COUL_EMPLOYES</t>
+  </si>
+  <si>
+    <t>Commande grossiste 200 flacons, compte pro salon coiffure, coffret entreprise, vente parfum (gagnee) - ILL_COUL_CRM_PISTES</t>
+  </si>
+  <si>
+    <t>3 parfums femme + 2 parfums homme + coffret cadeau (184 000 F CFA) - ILL_COUL_FACTURE_MAIL</t>
+  </si>
+  <si>
+    <t>PAIN &amp; GLACE</t>
+  </si>
+  <si>
+    <t>Boulangerie-glacier, Yopougon, Abidjan - prospect reel dont le comptable tient stock+compta sur Excel</t>
+  </si>
+  <si>
+    <t>res.company reelle - ILL_BOULANGERIE_SOCIETE</t>
+  </si>
+  <si>
+    <t>Stock (6 references)</t>
+  </si>
+  <si>
+    <t>Baguette, croissant, pain de mie, 2 glaces, sorbet - quantites reelles, remplace directement le suivi Excel - ILL_BOULANGERIE_STOCK</t>
+  </si>
+  <si>
+    <t>Commande grossiste hotel (baguettes + croissants + glace vanille, 91 000 F CFA) - ILL_BOULANGERIE_FACTURE_MAIL</t>
+  </si>
+  <si>
+    <t>MECANISME REEL D'ENVOI</t>
+  </si>
+  <si>
+    <t>Les 3 factures utilisent le vrai moteur email d'Odoo (account.email_template_edi_invoice + ir.mail_server reel OVH) - PDF genere par wkhtmltopdf, envoye a contact@ankrr.fr. Voir feuille Securite pour l'incident reel rencontre (rejet OVH) et sa correction.</t>
+  </si>
+  <si>
+    <t>REGLE IMPORTANTE (donnees permanentes)</t>
+  </si>
+  <si>
+    <t>Desinstaller un module Odoo supprime REELLEMENT ses tables SQL - mail, hr, crm, account, stock, hr_holidays, hr_recruitment restent donc actifs en PERMANENCE (voir MOD_ALL_CLEANUP_FINAL.sh) pour ne jamais perdre ce travail d'illustration.</t>
+  </si>
+  <si>
+    <t>Ce que gagne PAIN &amp; GLACE (et tout client similaire) avec la licence Enterprise</t>
+  </si>
+  <si>
+    <t>Deja vu en Community (gratuit)</t>
+  </si>
+  <si>
+    <t>Stock (6 references PAIN &amp; GLACE, remplace Excel) + Comptabilite (facture reelle envoyee par email)</t>
+  </si>
+  <si>
+    <t>Module Enterprise</t>
+  </si>
+  <si>
+    <t>Ce qu'il fait reellement</t>
+  </si>
+  <si>
+    <t>Pourquoi ca compte pour PAIN &amp; GLACE</t>
+  </si>
+  <si>
+    <t>accountant (Comptabilite complete)</t>
+  </si>
+  <si>
+    <t>Rapprochement bancaire automatise, liasse fiscale, tableaux de bord financiers</t>
+  </si>
+  <si>
+    <t>Le comptable ne ressaisit plus les releves bancaires a la main</t>
+  </si>
+  <si>
+    <t>stock_barcode (Codes-barres)</t>
+  </si>
+  <si>
+    <t>Inventaire au scanner, mouvements en 2 secondes</t>
+  </si>
+  <si>
+    <t>Comptage physique du stock sans ressaisie papier vers Excel</t>
+  </si>
+  <si>
+    <t>web_mobile (App Android/iPhone)</t>
+  </si>
+  <si>
+    <t>Application native, utilisable au comptoir, hors ligne</t>
+  </si>
+  <si>
+    <t>Consultation du stock ou saisie d'une vente depuis le telephone</t>
+  </si>
+  <si>
+    <t>planning (Planification)</t>
+  </si>
+  <si>
+    <t>Plannings du personnel visibles par tous</t>
+  </si>
+  <si>
+    <t>Remplace le planning papier affiche en cuisine</t>
+  </si>
+  <si>
+    <t>sign (Signature electronique)</t>
+  </si>
+  <si>
+    <t>Signature de documents a distance</t>
+  </si>
+  <si>
+    <t>Contrats fournisseurs (farine, lait) sans imprimer/scanner</t>
+  </si>
+  <si>
+    <t>appointment (RDV en ligne)</t>
+  </si>
+  <si>
+    <t>Reservation en ligne</t>
+  </si>
+  <si>
+    <t>Commande de gateau sur mesure sans appel telephonique</t>
+  </si>
+  <si>
+    <t>knowledge (Base de connaissances)</t>
+  </si>
+  <si>
+    <t>Recettes et procedures centralisees</t>
+  </si>
+  <si>
+    <t>Remplace les recettes sur cahier ou fichiers eparpilles</t>
+  </si>
+  <si>
+    <t>quality_control (Controle qualite)</t>
+  </si>
+  <si>
+    <t>Points de controle traces (temperature, DLC)</t>
+  </si>
+  <si>
+    <t>Tracabilite alimentaire reelle, utile en cas de controle sanitaire</t>
+  </si>
+  <si>
+    <t>timesheet_grid (Feuilles de temps)</t>
+  </si>
+  <si>
+    <t>Heures reellement travaillees, liees a la paie</t>
+  </si>
+  <si>
+    <t>Base reelle pour calculer les heures d'un employe</t>
+  </si>
+  <si>
+    <t>marketing_automation</t>
+  </si>
+  <si>
+    <t>Campagnes automatiques (relance client)</t>
+  </si>
+  <si>
+    <t>Fidelisation sans y penser chaque semaine</t>
+  </si>
+  <si>
+    <t>HONNETETE DU PROJET : le Community couvre deja l'essentiel demontre ici. L'Enterprise se justifie quand la douleur devient reelle et chiffrable (rapprochement bancaire manuel, ressaisie stock, paie a la main) - faire raconter cette douleur au client avant de proposer l'abonnement, jamais l'ordre inverse. Detail complet : docs/AVANTAGES_LICENCE_ENTERPRISE.md</t>
   </si>
   <si>
     <t>Vocabulaire - correspondance avec Control-M</t>
@@ -2312,7 +2577,7 @@
     <t>Memname / JOB_NAME</t>
   </si>
   <si>
-    <t>Colonne JOB_NAME de jobs_table.csv (ex: ECF_CRM_BLD_ACTIVATE) - convention ECF_&lt;MODULE&gt;_&lt;TIER&gt;_&lt;FONCTION&gt;</t>
+    <t>Colonne JOB_NAME (ex: ECF_CRM_BLD_ACTIVATE) - convention ECF_&lt;MODULE&gt;_&lt;TIER&gt;_&lt;FONCTION&gt;</t>
   </si>
   <si>
     <t>IN-condition</t>
@@ -2327,7 +2592,7 @@
     <t>Colonne OUT_COND - marque un fichier .ok dans state/ une fois le job reussi</t>
   </si>
   <si>
-    <t>AJP (Active Jobs File / Plan du jour)</t>
+    <t>AJP / Plan du jour</t>
   </si>
   <si>
     <t>jobs_table.csv + l'etat courant dans state/ (pas de notion de 'jour' - continu)</t>
@@ -2369,10 +2634,10 @@
     <t>Sysout</t>
   </si>
   <si>
-    <t>Log dedie a chaque execution dans state/history/&lt;JOB_ID&gt;/&lt;timestamp&gt;.log</t>
-  </si>
-  <si>
-    <t>Viewpoint / ecran d'exploitation</t>
+    <t>Log dedie dans state/history/&lt;JOB_ID&gt;/&lt;timestamp&gt;.log</t>
+  </si>
+  <si>
+    <t>Viewpoint</t>
   </si>
   <si>
     <t>./statut_live.sh + ce classeur Excel</t>
@@ -2381,13 +2646,16 @@
     <t>Tableau des jobs</t>
   </si>
   <si>
-    <t>jobs_table.csv - source de verite unique du projet</t>
+    <t>jobs_table.csv - source de verite unique</t>
+  </si>
+  <si>
+    <t>Securite, notifications et incidents reels</t>
   </si>
   <si>
     <t>Discipline des secrets</t>
   </si>
   <si>
-    <t>AUCUN mot de passe reel dans vars.conf ni dans aucun fichier versionne sur GitHub - toujours dans secrets/*.txt, chmod 600, exclu par .gitignore</t>
+    <t>AUCUN mot de passe reel dans vars.conf ni dans aucun fichier versionne sur GitHub - toujours secrets/*.txt, chmod 600, exclu par .gitignore</t>
   </si>
   <si>
     <t>Deposer le mot de passe SMTP</t>
@@ -2396,40 +2664,52 @@
     <t>echo -n 'mot_de_passe' &gt; ~/erp_crm_factory/secrets/smtp_password.txt &amp;&amp; chmod 600 ~/erp_crm_factory/secrets/smtp_password.txt</t>
   </si>
   <si>
-    <t>Alertes email</t>
-  </si>
-  <si>
-    <t>Actives (NOTIF_ENABLED=oui dans vars.conf) - envoyees automatiquement par orchestrator.sh a CHAQUE echec reel de job, jamais silencieux</t>
-  </si>
-  <si>
-    <t>Destinataire</t>
-  </si>
-  <si>
-    <t>contact@ankrr.fr, relais smtp.mail.ovh.net:465 (SSL)</t>
-  </si>
-  <si>
-    <t>Objet des mails</t>
-  </si>
-  <si>
-    <t>[ERP_CRM_FACTORY] ECHEC : &lt;JOB_ID&gt; sur &lt;machine&gt; - permet un tri automatique cote Outlook (regle a creer manuellement cote client : objet contient ERP_CRM_FACTORY)</t>
-  </si>
-  <si>
-    <t>Tester la config</t>
-  </si>
-  <si>
-    <t>./notifier.sh --test   (ou le job ODOO_SMTP_TEST)</t>
-  </si>
-  <si>
-    <t>Comptes/mots de passe reels de la demo</t>
-  </si>
-  <si>
-    <t>admin/admin (connexion web Odoo, a changer avant une vraie presentation client) - mot de passe maitre et mot de passe PostgreSQL generes aleatoirement, stockes uniquement dans secrets/ sur la VM</t>
-  </si>
-  <si>
-    <t>LeÃ§on reelle du 2026-09-01</t>
-  </si>
-  <si>
-    <t>Un chemin RELATIF dans une commande donnee a un operateur est une source d'erreur reelle (on ne sait jamais depuis quel repertoire il tape la commande) - toujours un chemin ABSOLU depuis le home (~/erp_crm_factory/...), coherent avec la destination documentee du clone.</t>
+    <t>Alertes email (echecs de job)</t>
+  </si>
+  <si>
+    <t>Actives - envoyees par orchestrator.sh a CHAQUE echec reel, objet [ERP_CRM_FACTORY]</t>
+  </si>
+  <si>
+    <t>Email sortant Odoo (factures)</t>
+  </si>
+  <si>
+    <t>Configure sur le vrai relais OVH (ODOO_MAIL_SERVER_REAL) - ir.mail_server + mail.alias.domain</t>
+  </si>
+  <si>
+    <t>Tester la config alertes</t>
+  </si>
+  <si>
+    <t>./notifier.sh --test</t>
+  </si>
+  <si>
+    <t>INCIDENT REEL DU 2026-09-01 (rejet OVH des factures)</t>
+  </si>
+  <si>
+    <t>Constat : OVH a renvoye 'Rejected by policy: From header domain does not align with authenticated domain'. Cause reelle (lue dans le code source Odoo, jamais supposee) : Odoo utilisait son repli code en dur 'OdooBot &lt;odoobot@example.com&gt;' comme expediteur, car aucune societe n'avait de mail.alias.domain configure. OVH exige que le domaine du From corresponde exactement au compte authentifie (contact@ankrr.fr) - politique anti-usurpation standard. Corrige a la racine (ODOO_MAIL_SERVER_REAL.sh) : mail.alias.domain='ankrr.fr' + default_from='contact', applique a TOUTES les societes - plus aucun email sortant ne peut retomber sur odoobot@example.com.</t>
+  </si>
+  <si>
+    <t>INCIDENT REEL - entrepot manquant</t>
+  </si>
+  <si>
+    <t>Une societe creee avant l'activation du module Stock n'a pas d'entrepot par defaut - cree explicitement dans ILL_BOULANGERIE_STOCK.sh (meme schema qu'Odoo utilise en interne).</t>
+  </si>
+  <si>
+    <t>INCIDENT REEL - plan comptable manquant</t>
+  </si>
+  <si>
+    <t>Une societe multi-entreprise n'a aucun journal comptable tant qu'un plan comptable ne lui est pas charge - env['account.chart.template'].try_loading('generic_coa', company) ajoute dans chaque job de facturation.</t>
+  </si>
+  <si>
+    <t>Comptes de la demo</t>
+  </si>
+  <si>
+    <t>Connexion web : admin/admin (a changer avant une vraie presentation client). Mot de passe maitre et PostgreSQL generes aleatoirement, stockes uniquement dans secrets/ sur la VM.</t>
+  </si>
+  <si>
+    <t>Lecon transversale du 2026-09-01</t>
+  </si>
+  <si>
+    <t>Un chemin RELATIF donne a un operateur est une source d'erreur reelle - toujours un chemin ABSOLU depuis le home (~/erp_crm_factory/...). Une reponse 'accepte par le serveur SMTP' n'est PAS une preuve de livraison reelle - le rejet peut arriver de facon asynchrone (bounce) apres coup ; verifier la boite de reception reelle reste la seule preuve definitive.</t>
   </si>
 </sst>
 </file>
@@ -2524,10 +2804,10 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2852,8 +3132,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D601004-A16F-4954-8CC1-F65060FD7971}">
-  <dimension ref="A1:B22"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA8BED1F-804A-46D2-B7E2-F5C0C831B1F9}">
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28.77734375" customWidth="1"/>
@@ -2930,7 +3210,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
@@ -2946,76 +3226,100 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B13" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
+    <row r="15" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B17" s="1" t="s">
         <v>26</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B23" s="1" t="s">
         <v>38</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -3027,9 +3331,112 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EE59217-FAAA-43C8-B601-CC336B4BB36C}">
+  <dimension ref="A1:B16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="30.77734375" customWidth="1"/>
+    <col min="2" max="2" width="70.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
+        <v>868</v>
+      </c>
+      <c r="B1" s="7"/>
+    </row>
+    <row r="2" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>869</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>873</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>875</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>877</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>881</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>883</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>885</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>888</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{521336EB-17D8-4C69-9324-51AD0C8422C9}">
-  <dimension ref="A1:A11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FFF15F7-B440-4A78-8C90-D55E263315D5}">
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="100.77734375" customWidth="1"/>
@@ -3037,52 +3444,62 @@
   <sheetData>
     <row r="1" spans="1:1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>39</v>
+      <c r="A2" s="4" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>40</v>
+      <c r="A3" s="4" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>42</v>
+      <c r="A4" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>45</v>
+      <c r="A6" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>47</v>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -3091,7 +3508,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F31272B1-5DA2-4ED2-BB75-359851638E27}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39E80B44-E9C2-441F-AB0C-062B7B261655}">
   <dimension ref="A1:A27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3100,122 +3517,122 @@
   <sheetData>
     <row r="1" spans="1:1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
-        <v>51</v>
+      <c r="A5" s="4" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
-        <v>52</v>
+      <c r="A6" s="4" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
-        <v>53</v>
+      <c r="A7" s="4" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
-        <v>54</v>
+      <c r="A8" s="4" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
-        <v>55</v>
+      <c r="A9" s="4" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
-        <v>56</v>
+      <c r="A10" s="4" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
-        <v>57</v>
+      <c r="A11" s="4" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
-        <v>58</v>
+      <c r="A12" s="4" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A15" s="5" t="s">
-        <v>52</v>
+      <c r="A15" s="4" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
-        <v>60</v>
+      <c r="A16" s="4" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="5" t="s">
-        <v>61</v>
+      <c r="A17" s="4" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" s="5" t="s">
-        <v>62</v>
+      <c r="A18" s="4" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" s="5" t="s">
-        <v>57</v>
+      <c r="A19" s="4" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" s="5" t="s">
-        <v>64</v>
+      <c r="A22" s="4" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" s="5" t="s">
-        <v>65</v>
+      <c r="A23" s="4" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24" s="5" t="s">
-        <v>66</v>
+      <c r="A24" s="4" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25" s="5" t="s">
-        <v>67</v>
+      <c r="A25" s="4" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A26" s="5" t="s">
-        <v>68</v>
+      <c r="A26" s="4" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A27" s="5" t="s">
-        <v>69</v>
+      <c r="A27" s="4" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -3224,7 +3641,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24F25DC0-A6E3-433F-8B8E-CFF87A382926}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCB49944-5B0C-4444-A63B-ED00F5B544C0}">
   <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3236,7 +3653,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -3245,602 +3662,602 @@
     </row>
     <row r="2" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>80</v>
+        <v>86</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>85</v>
+        <v>91</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>90</v>
+        <v>96</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>95</v>
+        <v>101</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>100</v>
+        <v>106</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>105</v>
+        <v>111</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>110</v>
+        <v>116</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>115</v>
+        <v>121</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>120</v>
+        <v>126</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>125</v>
+        <v>131</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>130</v>
+        <v>136</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>135</v>
+        <v>141</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>140</v>
+        <v>146</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>145</v>
+        <v>151</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>150</v>
+        <v>156</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>155</v>
+        <v>161</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>160</v>
+        <v>166</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>165</v>
+        <v>171</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>170</v>
+        <v>176</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>175</v>
+        <v>181</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>180</v>
+        <v>186</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>185</v>
+        <v>191</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>190</v>
+        <v>196</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>195</v>
+        <v>201</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>200</v>
+        <v>206</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>205</v>
+        <v>211</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>210</v>
+        <v>216</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>215</v>
+        <v>221</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>220</v>
+        <v>226</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>225</v>
+        <v>231</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>230</v>
+        <v>236</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>235</v>
+        <v>241</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>240</v>
+        <v>246</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>245</v>
+        <v>251</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="8" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
@@ -3853,11 +4270,12 @@
     <mergeCell ref="A37:E37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A46C8421-E8C3-4BED-8FBA-93E6F09B2E09}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{740EF00B-869A-4721-8D9F-146B18857963}">
   <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3868,168 +4286,168 @@
   <sheetData>
     <row r="1" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
     </row>
     <row r="2" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+        <v>260</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+        <v>263</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+        <v>266</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+        <v>269</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>265</v>
+        <v>272</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+        <v>278</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>274</v>
+        <v>281</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+        <v>284</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>280</v>
+        <v>287</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>283</v>
+        <v>290</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+        <v>293</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>289</v>
+        <v>296</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
@@ -4044,8 +4462,8 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4C3587F-A251-4AF3-9049-3B721A07E093}">
-  <dimension ref="A1:H100"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6C90DF5-FA46-4358-9031-856306C251F1}">
+  <dimension ref="A1:H106"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28.77734375" customWidth="1"/>
@@ -4059,7 +4477,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -4071,2700 +4489,3066 @@
     </row>
     <row r="2" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
-        <v>300</v>
+      <c r="A3" s="4" t="s">
+        <v>308</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>304</v>
+        <v>311</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>312</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
-        <v>308</v>
+      <c r="A4" s="4" t="s">
+        <v>316</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>310</v>
+        <v>311</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>318</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
-        <v>313</v>
+      <c r="A5" s="4" t="s">
+        <v>321</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>323</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
-        <v>318</v>
+      <c r="A6" s="4" t="s">
+        <v>326</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>320</v>
+        <v>311</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>328</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
-        <v>323</v>
+      <c r="A7" s="4" t="s">
+        <v>331</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>325</v>
+        <v>311</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>333</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
-        <v>328</v>
+      <c r="A8" s="4" t="s">
+        <v>336</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>330</v>
+        <v>311</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>338</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
-        <v>333</v>
+      <c r="A9" s="4" t="s">
+        <v>341</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>335</v>
+        <v>311</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>343</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
-        <v>338</v>
+      <c r="A10" s="4" t="s">
+        <v>346</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>340</v>
+        <v>311</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>348</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
-        <v>343</v>
+      <c r="A11" s="4" t="s">
+        <v>351</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>345</v>
+        <v>311</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>353</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
-        <v>348</v>
+      <c r="A12" s="4" t="s">
+        <v>356</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>350</v>
+        <v>311</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>358</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="5" t="s">
-        <v>353</v>
+      <c r="A13" s="4" t="s">
+        <v>361</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>355</v>
+        <v>311</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>363</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="5" t="s">
-        <v>358</v>
+      <c r="A14" s="4" t="s">
+        <v>366</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>360</v>
+        <v>311</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>368</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="5" t="s">
-        <v>363</v>
+      <c r="A15" s="4" t="s">
+        <v>371</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>365</v>
+        <v>311</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>373</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
-        <v>368</v>
+      <c r="A16" s="4" t="s">
+        <v>376</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>370</v>
+        <v>311</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>378</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="5" t="s">
-        <v>373</v>
+      <c r="A17" s="4" t="s">
+        <v>381</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>375</v>
+        <v>311</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>383</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="5" t="s">
-        <v>378</v>
+      <c r="A18" s="4" t="s">
+        <v>386</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>380</v>
+        <v>311</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>388</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="5" t="s">
-        <v>383</v>
+      <c r="A19" s="4" t="s">
+        <v>391</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>385</v>
+        <v>311</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>393</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="5" t="s">
-        <v>388</v>
+      <c r="A20" s="4" t="s">
+        <v>396</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>390</v>
+        <v>311</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>398</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="5" t="s">
-        <v>393</v>
+      <c r="A21" s="4" t="s">
+        <v>401</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>395</v>
+        <v>311</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>403</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="5" t="s">
-        <v>398</v>
+      <c r="A22" s="4" t="s">
+        <v>406</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>400</v>
+        <v>311</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>408</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A23" s="5" t="s">
-        <v>79</v>
+      <c r="A23" s="4" t="s">
+        <v>87</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>404</v>
+        <v>311</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>412</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A24" s="5" t="s">
-        <v>80</v>
+      <c r="A24" s="4" t="s">
+        <v>88</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>408</v>
+        <v>311</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>416</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="H24" s="1" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="G25" s="1" t="s">
         <v>410</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>412</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>402</v>
-      </c>
       <c r="H25" s="1" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A26" s="5" t="s">
-        <v>85</v>
+      <c r="A26" s="4" t="s">
+        <v>93</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>416</v>
+        <v>311</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>424</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="5" t="s">
-        <v>89</v>
+      <c r="A27" s="4" t="s">
+        <v>97</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>420</v>
+        <v>311</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>428</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="5" t="s">
-        <v>90</v>
+      <c r="A28" s="4" t="s">
+        <v>98</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>424</v>
+        <v>311</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>432</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A29" s="5" t="s">
-        <v>94</v>
+      <c r="A29" s="4" t="s">
+        <v>102</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>428</v>
+        <v>311</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>436</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A30" s="5" t="s">
-        <v>95</v>
+      <c r="A30" s="4" t="s">
+        <v>103</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>432</v>
+        <v>311</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>440</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>434</v>
+        <v>442</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A31" s="5" t="s">
-        <v>99</v>
+      <c r="A31" s="4" t="s">
+        <v>107</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>436</v>
+        <v>311</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>444</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A32" s="5" t="s">
-        <v>100</v>
+      <c r="A32" s="4" t="s">
+        <v>108</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>440</v>
+        <v>311</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>448</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>442</v>
+        <v>450</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" s="5" t="s">
-        <v>104</v>
+      <c r="A33" s="4" t="s">
+        <v>112</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>444</v>
+        <v>311</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>452</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A34" s="5" t="s">
-        <v>105</v>
+      <c r="A34" s="4" t="s">
+        <v>113</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>448</v>
+        <v>311</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>456</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A35" s="5" t="s">
-        <v>109</v>
+      <c r="A35" s="4" t="s">
+        <v>117</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>452</v>
+        <v>311</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>460</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A36" s="5" t="s">
-        <v>110</v>
+      <c r="A36" s="4" t="s">
+        <v>118</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>456</v>
+        <v>311</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>464</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="5" t="s">
-        <v>114</v>
+      <c r="A37" s="4" t="s">
+        <v>122</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>460</v>
+        <v>311</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>468</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A38" s="5" t="s">
-        <v>115</v>
+      <c r="A38" s="4" t="s">
+        <v>123</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>464</v>
+        <v>311</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>472</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39" s="5" t="s">
-        <v>119</v>
+      <c r="A39" s="4" t="s">
+        <v>127</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>468</v>
+        <v>311</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>476</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A40" s="5" t="s">
-        <v>120</v>
+      <c r="A40" s="4" t="s">
+        <v>128</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>472</v>
+        <v>311</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>480</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>474</v>
+        <v>482</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" s="5" t="s">
-        <v>124</v>
+      <c r="A41" s="4" t="s">
+        <v>132</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>476</v>
+        <v>311</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>484</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42" s="5" t="s">
-        <v>125</v>
+      <c r="A42" s="4" t="s">
+        <v>133</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>480</v>
+        <v>311</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>488</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A43" s="5" t="s">
-        <v>129</v>
+      <c r="A43" s="4" t="s">
+        <v>137</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>484</v>
+        <v>311</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>492</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A44" s="5" t="s">
-        <v>130</v>
+      <c r="A44" s="4" t="s">
+        <v>138</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>488</v>
+        <v>311</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>496</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A45" s="5" t="s">
-        <v>134</v>
+      <c r="A45" s="4" t="s">
+        <v>142</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E45" s="5" t="s">
-        <v>492</v>
+        <v>311</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>500</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A46" s="5" t="s">
-        <v>135</v>
+      <c r="A46" s="4" t="s">
+        <v>143</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E46" s="5" t="s">
-        <v>496</v>
+        <v>311</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>504</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A47" s="5" t="s">
-        <v>139</v>
+      <c r="A47" s="4" t="s">
+        <v>147</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E47" s="5" t="s">
-        <v>500</v>
+        <v>311</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>508</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A48" s="5" t="s">
-        <v>140</v>
+      <c r="A48" s="4" t="s">
+        <v>148</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E48" s="5" t="s">
-        <v>504</v>
+        <v>311</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>512</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>506</v>
+        <v>514</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A49" s="5" t="s">
-        <v>144</v>
+      <c r="A49" s="4" t="s">
+        <v>152</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E49" s="5" t="s">
-        <v>508</v>
+        <v>311</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>516</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A50" s="5" t="s">
-        <v>145</v>
+      <c r="A50" s="4" t="s">
+        <v>153</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E50" s="5" t="s">
-        <v>512</v>
+        <v>311</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>520</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>514</v>
+        <v>522</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A51" s="5" t="s">
-        <v>149</v>
+      <c r="A51" s="4" t="s">
+        <v>157</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E51" s="5" t="s">
-        <v>516</v>
+        <v>311</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>524</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A52" s="5" t="s">
-        <v>150</v>
+      <c r="A52" s="4" t="s">
+        <v>158</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E52" s="5" t="s">
-        <v>520</v>
+        <v>311</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>528</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>522</v>
+        <v>530</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A53" s="5" t="s">
-        <v>154</v>
+      <c r="A53" s="4" t="s">
+        <v>162</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E53" s="5" t="s">
-        <v>524</v>
+        <v>311</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>532</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>526</v>
+        <v>534</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A54" s="5" t="s">
-        <v>155</v>
+      <c r="A54" s="4" t="s">
+        <v>163</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E54" s="5" t="s">
-        <v>528</v>
+        <v>311</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>536</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>530</v>
+        <v>538</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A55" s="5" t="s">
-        <v>159</v>
+      <c r="A55" s="4" t="s">
+        <v>167</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E55" s="5" t="s">
-        <v>532</v>
+        <v>311</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>540</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A56" s="5" t="s">
-        <v>160</v>
+      <c r="A56" s="4" t="s">
+        <v>168</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E56" s="5" t="s">
-        <v>536</v>
+        <v>311</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>544</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A57" s="5" t="s">
-        <v>164</v>
+      <c r="A57" s="4" t="s">
+        <v>172</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E57" s="5" t="s">
-        <v>540</v>
+        <v>311</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>548</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>542</v>
+        <v>550</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A58" s="5" t="s">
-        <v>165</v>
+      <c r="A58" s="4" t="s">
+        <v>173</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E58" s="5" t="s">
-        <v>544</v>
+        <v>311</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>552</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>546</v>
+        <v>554</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A59" s="5" t="s">
-        <v>169</v>
+      <c r="A59" s="4" t="s">
+        <v>177</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E59" s="5" t="s">
-        <v>548</v>
+        <v>311</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>556</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>550</v>
+        <v>558</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A60" s="5" t="s">
-        <v>170</v>
+      <c r="A60" s="4" t="s">
+        <v>178</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>551</v>
+        <v>559</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E60" s="5" t="s">
-        <v>552</v>
+        <v>311</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>560</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>554</v>
+        <v>562</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A61" s="5" t="s">
-        <v>174</v>
+      <c r="A61" s="4" t="s">
+        <v>182</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>555</v>
+        <v>563</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E61" s="5" t="s">
-        <v>556</v>
+        <v>311</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>564</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A62" s="5" t="s">
-        <v>175</v>
+      <c r="A62" s="4" t="s">
+        <v>183</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>559</v>
+        <v>567</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E62" s="5" t="s">
-        <v>560</v>
+        <v>311</v>
+      </c>
+      <c r="E62" s="4" t="s">
+        <v>568</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>561</v>
+        <v>569</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>562</v>
+        <v>570</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A63" s="5" t="s">
-        <v>179</v>
+      <c r="A63" s="4" t="s">
+        <v>187</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>563</v>
+        <v>571</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E63" s="5" t="s">
-        <v>564</v>
+        <v>311</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>572</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>565</v>
+        <v>573</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>566</v>
+        <v>574</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A64" s="5" t="s">
-        <v>180</v>
+      <c r="A64" s="4" t="s">
+        <v>188</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E64" s="5" t="s">
-        <v>568</v>
+        <v>311</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>576</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>566</v>
+        <v>574</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>570</v>
+        <v>578</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A65" s="5" t="s">
-        <v>184</v>
+      <c r="A65" s="4" t="s">
+        <v>192</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E65" s="5" t="s">
-        <v>572</v>
+        <v>311</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>580</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A66" s="5" t="s">
-        <v>185</v>
+      <c r="A66" s="4" t="s">
+        <v>193</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>575</v>
+        <v>583</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E66" s="5" t="s">
-        <v>576</v>
+        <v>311</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>584</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>577</v>
+        <v>585</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>578</v>
+        <v>586</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A67" s="5" t="s">
-        <v>189</v>
+      <c r="A67" s="4" t="s">
+        <v>197</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E67" s="5" t="s">
-        <v>580</v>
+        <v>311</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>588</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>582</v>
+        <v>590</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A68" s="5" t="s">
-        <v>190</v>
+      <c r="A68" s="4" t="s">
+        <v>198</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E68" s="5" t="s">
-        <v>584</v>
+        <v>311</v>
+      </c>
+      <c r="E68" s="4" t="s">
+        <v>592</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A69" s="5" t="s">
-        <v>194</v>
+      <c r="A69" s="4" t="s">
+        <v>202</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>587</v>
+        <v>595</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E69" s="5" t="s">
-        <v>588</v>
+        <v>311</v>
+      </c>
+      <c r="E69" s="4" t="s">
+        <v>596</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>590</v>
+        <v>598</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A70" s="5" t="s">
-        <v>195</v>
+      <c r="A70" s="4" t="s">
+        <v>203</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E70" s="5" t="s">
-        <v>592</v>
+        <v>311</v>
+      </c>
+      <c r="E70" s="4" t="s">
+        <v>600</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>594</v>
+        <v>602</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A71" s="5" t="s">
-        <v>199</v>
+      <c r="A71" s="4" t="s">
+        <v>207</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>595</v>
+        <v>603</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E71" s="5" t="s">
-        <v>596</v>
+        <v>311</v>
+      </c>
+      <c r="E71" s="4" t="s">
+        <v>604</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>597</v>
+        <v>605</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>598</v>
+        <v>606</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A72" s="5" t="s">
-        <v>200</v>
+      <c r="A72" s="4" t="s">
+        <v>208</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E72" s="5" t="s">
-        <v>600</v>
+        <v>311</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>608</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>598</v>
+        <v>606</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>602</v>
+        <v>610</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A73" s="5" t="s">
-        <v>204</v>
+      <c r="A73" s="4" t="s">
+        <v>212</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>603</v>
+        <v>611</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E73" s="5" t="s">
-        <v>604</v>
+        <v>311</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>612</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>605</v>
+        <v>613</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>606</v>
+        <v>614</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A74" s="5" t="s">
-        <v>205</v>
+      <c r="A74" s="4" t="s">
+        <v>213</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>607</v>
+        <v>615</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E74" s="5" t="s">
-        <v>608</v>
+        <v>311</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>616</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>609</v>
+        <v>617</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>606</v>
+        <v>614</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>610</v>
+        <v>618</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A75" s="5" t="s">
-        <v>209</v>
+      <c r="A75" s="4" t="s">
+        <v>217</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>611</v>
+        <v>619</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E75" s="5" t="s">
-        <v>612</v>
+        <v>311</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>620</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>613</v>
+        <v>621</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>614</v>
+        <v>622</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A76" s="5" t="s">
-        <v>210</v>
+      <c r="A76" s="4" t="s">
+        <v>218</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E76" s="5" t="s">
-        <v>616</v>
+        <v>311</v>
+      </c>
+      <c r="E76" s="4" t="s">
+        <v>624</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>617</v>
+        <v>625</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>614</v>
+        <v>622</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A77" s="5" t="s">
-        <v>214</v>
+      <c r="A77" s="4" t="s">
+        <v>222</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E77" s="5" t="s">
-        <v>620</v>
+        <v>311</v>
+      </c>
+      <c r="E77" s="4" t="s">
+        <v>628</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>622</v>
+        <v>630</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A78" s="5" t="s">
-        <v>215</v>
+      <c r="A78" s="4" t="s">
+        <v>223</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E78" s="5" t="s">
-        <v>624</v>
+        <v>311</v>
+      </c>
+      <c r="E78" s="4" t="s">
+        <v>632</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>625</v>
+        <v>633</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>622</v>
+        <v>630</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>626</v>
+        <v>634</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A79" s="5" t="s">
-        <v>219</v>
+      <c r="A79" s="4" t="s">
+        <v>227</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E79" s="5" t="s">
-        <v>628</v>
+        <v>311</v>
+      </c>
+      <c r="E79" s="4" t="s">
+        <v>636</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>630</v>
+        <v>638</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A80" s="5" t="s">
-        <v>220</v>
+      <c r="A80" s="4" t="s">
+        <v>228</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>631</v>
+        <v>639</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E80" s="5" t="s">
-        <v>632</v>
+        <v>311</v>
+      </c>
+      <c r="E80" s="4" t="s">
+        <v>640</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>633</v>
+        <v>641</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>630</v>
+        <v>638</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>634</v>
+        <v>642</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A81" s="5" t="s">
-        <v>224</v>
+      <c r="A81" s="4" t="s">
+        <v>232</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>635</v>
+        <v>643</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E81" s="5" t="s">
-        <v>636</v>
+        <v>311</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>644</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>637</v>
+        <v>645</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>638</v>
+        <v>646</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A82" s="5" t="s">
-        <v>225</v>
+      <c r="A82" s="4" t="s">
+        <v>233</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>639</v>
+        <v>647</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E82" s="5" t="s">
-        <v>640</v>
+        <v>311</v>
+      </c>
+      <c r="E82" s="4" t="s">
+        <v>648</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>641</v>
+        <v>649</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>638</v>
+        <v>646</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>642</v>
+        <v>650</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A83" s="5" t="s">
-        <v>229</v>
+      <c r="A83" s="4" t="s">
+        <v>237</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>643</v>
+        <v>651</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E83" s="5" t="s">
-        <v>644</v>
+        <v>311</v>
+      </c>
+      <c r="E83" s="4" t="s">
+        <v>652</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>645</v>
+        <v>653</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>646</v>
+        <v>654</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A84" s="5" t="s">
-        <v>230</v>
+      <c r="A84" s="4" t="s">
+        <v>238</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>647</v>
+        <v>655</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E84" s="5" t="s">
-        <v>648</v>
+        <v>311</v>
+      </c>
+      <c r="E84" s="4" t="s">
+        <v>656</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>649</v>
+        <v>657</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>646</v>
+        <v>654</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>650</v>
+        <v>658</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A85" s="5" t="s">
-        <v>234</v>
+      <c r="A85" s="4" t="s">
+        <v>242</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>651</v>
+        <v>659</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E85" s="5" t="s">
-        <v>652</v>
+        <v>311</v>
+      </c>
+      <c r="E85" s="4" t="s">
+        <v>660</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>653</v>
+        <v>661</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>654</v>
+        <v>662</v>
       </c>
     </row>
     <row r="86" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A86" s="5" t="s">
-        <v>235</v>
+      <c r="A86" s="4" t="s">
+        <v>243</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>655</v>
+        <v>663</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E86" s="5" t="s">
-        <v>656</v>
+        <v>311</v>
+      </c>
+      <c r="E86" s="4" t="s">
+        <v>664</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>657</v>
+        <v>665</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>654</v>
+        <v>662</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>658</v>
+        <v>666</v>
       </c>
     </row>
     <row r="87" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A87" s="5" t="s">
-        <v>239</v>
+      <c r="A87" s="4" t="s">
+        <v>247</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>659</v>
+        <v>667</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E87" s="5" t="s">
-        <v>660</v>
+        <v>311</v>
+      </c>
+      <c r="E87" s="4" t="s">
+        <v>668</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>661</v>
+        <v>669</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>662</v>
+        <v>670</v>
       </c>
     </row>
     <row r="88" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A88" s="5" t="s">
-        <v>240</v>
+      <c r="A88" s="4" t="s">
+        <v>248</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>663</v>
+        <v>671</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E88" s="5" t="s">
-        <v>664</v>
+        <v>311</v>
+      </c>
+      <c r="E88" s="4" t="s">
+        <v>672</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>665</v>
+        <v>673</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>662</v>
+        <v>670</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>666</v>
+        <v>674</v>
       </c>
     </row>
     <row r="89" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A89" s="5" t="s">
-        <v>244</v>
+      <c r="A89" s="4" t="s">
+        <v>252</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>667</v>
+        <v>675</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E89" s="5" t="s">
-        <v>668</v>
+        <v>311</v>
+      </c>
+      <c r="E89" s="4" t="s">
+        <v>676</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>669</v>
+        <v>677</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
     </row>
     <row r="90" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A90" s="5" t="s">
-        <v>245</v>
+      <c r="A90" s="4" t="s">
+        <v>253</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>671</v>
+        <v>679</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E90" s="5" t="s">
-        <v>672</v>
+        <v>311</v>
+      </c>
+      <c r="E90" s="4" t="s">
+        <v>680</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>673</v>
+        <v>681</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>674</v>
+        <v>682</v>
       </c>
     </row>
     <row r="91" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A91" s="5" t="s">
-        <v>675</v>
+      <c r="A91" s="4" t="s">
+        <v>683</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>676</v>
+        <v>684</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E91" s="5" t="s">
-        <v>677</v>
+        <v>311</v>
+      </c>
+      <c r="E91" s="4" t="s">
+        <v>685</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>678</v>
+        <v>686</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>674</v>
+        <v>682</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>679</v>
+        <v>687</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A92" s="5" t="s">
-        <v>680</v>
+      <c r="A92" s="4" t="s">
+        <v>688</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>681</v>
+        <v>689</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E92" s="5" t="s">
-        <v>682</v>
+        <v>311</v>
+      </c>
+      <c r="E92" s="4" t="s">
+        <v>690</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>683</v>
+        <v>691</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>684</v>
+        <v>692</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A93" s="5" t="s">
-        <v>685</v>
+      <c r="A93" s="4" t="s">
+        <v>693</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>686</v>
+        <v>694</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E93" s="5" t="s">
-        <v>687</v>
+        <v>311</v>
+      </c>
+      <c r="E93" s="4" t="s">
+        <v>695</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>688</v>
+        <v>696</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>689</v>
+        <v>697</v>
       </c>
     </row>
     <row r="94" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A94" s="5" t="s">
-        <v>690</v>
+      <c r="A94" s="4" t="s">
+        <v>698</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E94" s="5" t="s">
-        <v>692</v>
+        <v>311</v>
+      </c>
+      <c r="E94" s="4" t="s">
+        <v>700</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>693</v>
+        <v>701</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>694</v>
+        <v>702</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>695</v>
+        <v>703</v>
       </c>
     </row>
     <row r="95" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A95" s="5" t="s">
-        <v>696</v>
+      <c r="A95" s="4" t="s">
+        <v>704</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E95" s="5" t="s">
-        <v>698</v>
+        <v>311</v>
+      </c>
+      <c r="E95" s="4" t="s">
+        <v>706</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>699</v>
+        <v>707</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>700</v>
+        <v>708</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
     </row>
     <row r="96" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A96" s="5" t="s">
-        <v>702</v>
+      <c r="A96" s="4" t="s">
+        <v>710</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>703</v>
+        <v>711</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E96" s="5" t="s">
-        <v>704</v>
+        <v>311</v>
+      </c>
+      <c r="E96" s="4" t="s">
+        <v>712</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>705</v>
+        <v>713</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>706</v>
+        <v>714</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>707</v>
+        <v>715</v>
       </c>
     </row>
     <row r="97" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A97" s="5" t="s">
-        <v>708</v>
+      <c r="A97" s="4" t="s">
+        <v>716</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>709</v>
+        <v>717</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E97" s="5" t="s">
-        <v>710</v>
+        <v>311</v>
+      </c>
+      <c r="E97" s="4" t="s">
+        <v>718</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>711</v>
+        <v>719</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>712</v>
+        <v>720</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>713</v>
+        <v>721</v>
       </c>
     </row>
     <row r="98" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A98" s="5" t="s">
-        <v>714</v>
+      <c r="A98" s="4" t="s">
+        <v>722</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>715</v>
+        <v>723</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E98" s="5" t="s">
-        <v>716</v>
+        <v>311</v>
+      </c>
+      <c r="E98" s="4" t="s">
+        <v>724</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>717</v>
+        <v>725</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>718</v>
+        <v>726</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>719</v>
+        <v>727</v>
       </c>
     </row>
     <row r="99" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A99" s="5" t="s">
-        <v>720</v>
+      <c r="A99" s="4" t="s">
+        <v>728</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>721</v>
+        <v>729</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E99" s="5" t="s">
-        <v>722</v>
+        <v>311</v>
+      </c>
+      <c r="E99" s="4" t="s">
+        <v>730</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A100" s="5" t="s">
-        <v>726</v>
+      <c r="A100" s="4" t="s">
+        <v>734</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>727</v>
+        <v>735</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E100" s="5" t="s">
-        <v>728</v>
+        <v>311</v>
+      </c>
+      <c r="E100" s="4" t="s">
+        <v>736</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>729</v>
+        <v>737</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>730</v>
+        <v>738</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A101" s="4" t="s">
+        <v>739</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="E101" s="4" t="s">
+        <v>741</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="H101" s="1" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A102" s="4" t="s">
+        <v>744</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="E102" s="4" t="s">
+        <v>746</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="G102" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="H102" s="1" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A103" s="4" t="s">
+        <v>750</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="E103" s="4" t="s">
+        <v>752</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="H103" s="1" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A104" s="4" t="s">
+        <v>756</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="E104" s="4" t="s">
+        <v>758</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="H104" s="1" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A105" s="4" t="s">
+        <v>761</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>762</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="E105" s="4" t="s">
+        <v>763</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>764</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="H105" s="1" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A106" s="4" t="s">
+        <v>767</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="E106" s="4" t="s">
+        <v>769</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="G106" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="H106" s="1" t="s">
+        <v>772</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3100EBA1-3EC6-4078-A42A-45F78C5B455D}">
+  <dimension ref="A1:B21"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="24.77734375" customWidth="1"/>
+    <col min="2" max="2" width="76.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
+        <v>773</v>
+      </c>
+      <c r="B1" s="7"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>774</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>776</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>778</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>780</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>782</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>784</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>776</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>780</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>784</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>776</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>796</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>784</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>799</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>801</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>802</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B65C4E24-2072-4762-B061-91BD62466E18}">
-  <dimension ref="A1:B14"/>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB231983-C483-4880-BF8F-1DAE69FC51E8}">
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.77734375" customWidth="1"/>
-    <col min="2" max="2" width="78.77734375" customWidth="1"/>
+    <col min="2" max="2" width="45.77734375" customWidth="1"/>
+    <col min="3" max="3" width="55.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>731</v>
+        <v>803</v>
       </c>
       <c r="B1" s="7"/>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C1" s="7"/>
+    </row>
+    <row r="2" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>732</v>
+        <v>804</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>734</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>736</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>738</v>
+        <v>805</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
+        <v>806</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>807</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>809</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>740</v>
+        <v>810</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>812</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>742</v>
+        <v>813</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>815</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+        <v>816</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>819</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>744</v>
+        <v>821</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>734</v>
+        <v>822</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>824</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>747</v>
+        <v>825</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>827</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>738</v>
+        <v>828</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>830</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
+        <v>831</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>834</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>750</v>
+        <v>836</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>751</v>
-      </c>
+        <v>837</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="8" t="s">
+        <v>839</v>
+      </c>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A16:C16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39DC8B9B-96F5-4EEC-A375-9A7AA0F9116C}">
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA9DD675-0ED8-446E-9420-841FCD9A084F}">
   <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -6774,207 +7558,120 @@
   <sheetData>
     <row r="1" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>752</v>
+        <v>840</v>
       </c>
       <c r="B1" s="7"/>
     </row>
     <row r="2" spans="1:2" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>753</v>
+        <v>841</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>754</v>
+        <v>842</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>755</v>
+        <v>843</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>756</v>
+        <v>844</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>757</v>
+        <v>845</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>758</v>
+        <v>846</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>759</v>
+        <v>847</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>760</v>
+        <v>848</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>761</v>
+        <v>849</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>762</v>
+        <v>850</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>763</v>
+        <v>851</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>764</v>
+        <v>852</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>765</v>
+        <v>853</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>766</v>
+        <v>854</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>767</v>
+        <v>855</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>768</v>
+        <v>856</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>769</v>
+        <v>857</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>770</v>
+        <v>858</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>771</v>
+        <v>859</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>772</v>
+        <v>860</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>773</v>
+        <v>861</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>774</v>
+        <v>862</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>775</v>
+        <v>863</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>776</v>
+        <v>864</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>777</v>
+        <v>865</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>778</v>
+        <v>866</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>779</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB6F1224-6429-440E-860B-963FDC3C7720}">
-  <dimension ref="A1:B12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="30.77734375" customWidth="1"/>
-    <col min="2" max="2" width="70.77734375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B1" s="7"/>
-    </row>
-    <row r="2" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>780</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>782</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>783</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>784</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>786</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>787</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>788</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>790</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>792</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>793</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>794</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>795</v>
+        <v>867</v>
       </c>
     </row>
   </sheetData>

--- a/TABLEAU_DE_BORD_EXPLOITATION.xlsx
+++ b/TABLEAU_DE_BORD_EXPLOITATION.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HPPROB~1\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{49C7293E-F9C8-4961-8178-DE0E4FFFFFE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B72DE7FF-7822-4EAE-9609-367B24F86CB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2472" yWindow="2472" windowWidth="17280" windowHeight="8880" xr2:uid="{9F4751C8-6260-474C-A39A-B9631EA72652}"/>
+    <workbookView xWindow="2472" yWindow="2472" windowWidth="17280" windowHeight="8880" xr2:uid="{1246B937-30C5-4A85-B842-22076B5D7E7F}"/>
   </bookViews>
   <sheets>
     <sheet name="Vue d'ensemble" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1265" uniqueCount="889">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1264" uniqueCount="888">
   <si>
     <t>ERP_CRM_FACTORY - Tableau de bord d'exploitation</t>
   </si>
@@ -78,10 +78,7 @@
     <t>Meme orchestrateur bash que WAZ_ELK_FACTORY (jobs_table.csv, IN_COND/OUT_COND) - reutilise tel quel, projet volontairement autonome</t>
   </si>
   <si>
-    <t>ETAT REEL AU 2026-09-01 (soir)</t>
-  </si>
-  <si>
-    <t>(verifie en base a chaque etape, jamais suppose - voir docs/JOURNAL_TECHNIQUE.md)</t>
+    <t>ETAT REEL AU 2026-09-02 (verifie a chaque etape, jamais suppose)</t>
   </si>
   <si>
     <t>Tier 0</t>
@@ -99,7 +96,7 @@
     <t>Tier 2</t>
   </si>
   <si>
-    <t>16 jobs - illustrations personnalisees CLIM AUTO / COUL / PAIN &amp; GLACE (RH + CRM + Stock + Factures envoyees par email), verifiees en base</t>
+    <t>16 jobs - illustrations CLIM AUTO / COUL / PAIN &amp; GLACE (RH, CRM, Stock, Factures PDF+email)</t>
   </si>
   <si>
     <t>Notifications</t>
@@ -111,21 +108,30 @@
     <t>Email sortant Odoo</t>
   </si>
   <si>
-    <t>Configure sur le vrai relais OVH - voir feuille Securite pour l'incident reel et sa correction</t>
+    <t>Relais OVH reel configure - voir feuille Securite pour l'incident et sa correction</t>
+  </si>
+  <si>
+    <t>Facture PDF</t>
+  </si>
+  <si>
+    <t>Generee par le vrai moteur Odoo (wkhtmltopdf), identique a une facture Orange/MTN</t>
+  </si>
+  <si>
+    <t>Deploiement verifie depuis GitHub</t>
+  </si>
+  <si>
+    <t>git clone reel + orchestrateur complet -&gt; TERMINE SANS ECHEC (2026-09-02)</t>
   </si>
   <si>
     <t>REGLE D'OR POUR LE PILOTE</t>
   </si>
   <si>
-    <t>Chaque job de ce classeur qui touche Odoo passe par le VRAI moteur Odoo (ORM, meme code qu'un clic reel dans l'interface web) - ce qui se joue en CLI se voit IMMEDIATEMENT dans l'interface web (https://erp.odoo.local/), jamais une simulation separee.</t>
+    <t>Chaque job qui touche Odoo passe par le VRAI moteur Odoo (ORM, meme code qu'un clic reel dans l'interface web) - ce qui se joue en CLI se voit IMMEDIATEMENT dans l'interface web (https://erp.odoo.local/), jamais une simulation separee.</t>
   </si>
   <si>
     <t>Structure de ce classeur</t>
   </si>
   <si>
-    <t>chaque feuille ci-dessous, faÃ§on Control-M reel</t>
-  </si>
-  <si>
     <t>Demarrage rapide</t>
   </si>
   <si>
@@ -153,13 +159,13 @@
     <t>Reference complete des jobs</t>
   </si>
   <si>
-    <t>tous les jobs du projet, un par ligne, generes depuis jobs_table.csv</t>
+    <t>tous les jobs du projet, generes depuis jobs_table.csv</t>
   </si>
   <si>
     <t>Illustrations 3 entreprises</t>
   </si>
   <si>
-    <t>CLIM AUTO, COUL, PAIN &amp; GLACE - RH, CRM, stock, factures envoyees par email</t>
+    <t>CLIM AUTO, COUL, PAIN &amp; GLACE - RH, CRM, stock, factures PDF+email</t>
   </si>
   <si>
     <t>Avantages licence Enterprise</t>
@@ -210,13 +216,13 @@
     <t>10. Voir le statut a tout moment : ./statut_live.sh</t>
   </si>
   <si>
-    <t>Destination du clone toujours identique : ~/erp_crm_factory (le 'cd ~' initial est volontaire - jamais un chemin qui depend du repertoire de depart).</t>
+    <t>Destination du clone toujours identique : ~/erp_crm_factory. Deploiement verifie reellement de bout en bout depuis GitHub le 2026-09-02 : TERMINE SANS ECHEC.</t>
   </si>
   <si>
     <t>Connexion GitHub - procedure complete</t>
   </si>
   <si>
-    <t>Depot : https://github.com/ykeupssi123-ship-it/ECF (verifier la visibilite avant transmission a un tiers)</t>
+    <t>Depot : https://github.com/ykeupssi123-ship-it/ECF</t>
   </si>
   <si>
     <t>A. Cas normal - cloner directement sur la VM Linux</t>
@@ -234,7 +240,7 @@
     <t>cd erp_crm_factory</t>
   </si>
   <si>
-    <t>git status   (doit afficher 'nothing to commit, working tree clean' - ne jamais continuer sur un clone partiel)</t>
+    <t>git status</t>
   </si>
   <si>
     <t>find . -name '*.sh' | wc -l</t>
@@ -246,7 +252,7 @@
     <t>./orchestrator.sh</t>
   </si>
   <si>
-    <t>B. Alternative sans git (installation refusee/impossible)</t>
+    <t>B. Alternative sans git</t>
   </si>
   <si>
     <t>curl -L -o ECF.zip https://github.com/ykeupssi123-ship-it/ECF/archive/refs/heads/main.zip</t>
@@ -276,10 +282,10 @@
     <t>4. git clone https://github.com/SON-COMPTE/ECF.git</t>
   </si>
   <si>
-    <t>5. Push : GitHub demande un token (Settings -&gt; Developer settings -&gt; Personal access tokens), jamais le mot de passe du compte</t>
-  </si>
-  <si>
-    <t>Catalogue des 34 modules Community reels (verifie en base le 2026-09-01)</t>
+    <t>5. Push : token requis (Settings -&gt; Developer settings -&gt; Personal access tokens)</t>
+  </si>
+  <si>
+    <t>Catalogue des 34 modules Community reels (verifie en base)</t>
   </si>
   <si>
     <t>Code</t>
@@ -333,7 +339,7 @@
     <t>mail</t>
   </si>
   <si>
-    <t>Messagerie interne - RESTE ACTIF EN PERMANENCE (infrastructure)</t>
+    <t>Messagerie interne - RESTE ACTIF (infrastructure)</t>
   </si>
   <si>
     <t>MOD_DISCUSS_ACTIVATE</t>
@@ -348,7 +354,7 @@
     <t>crm</t>
   </si>
   <si>
-    <t>Suivi des pistes et opportunites - RESTE ACTIF (porte CLIM AUTO/COUL)</t>
+    <t>Suivi des pistes - RESTE ACTIF (CLIM AUTO/COUL)</t>
   </si>
   <si>
     <t>MOD_CRM_ACTIVATE</t>
@@ -378,7 +384,7 @@
     <t>account</t>
   </si>
   <si>
-    <t>Facturation et comptabilite - RESTE ACTIF (porte les factures reelles)</t>
+    <t>Comptabilite - RESTE ACTIF (factures reelles)</t>
   </si>
   <si>
     <t>MOD_COMPTA_ACTIVATE</t>
@@ -408,7 +414,7 @@
     <t>stock</t>
   </si>
   <si>
-    <t>Gestion des stocks - RESTE ACTIF (porte le stock PAIN &amp; GLACE)</t>
+    <t>Stock - RESTE ACTIF (PAIN &amp; GLACE)</t>
   </si>
   <si>
     <t>MOD_STOCK_ACTIVATE</t>
@@ -573,7 +579,7 @@
     <t>hr</t>
   </si>
   <si>
-    <t>Fiches employes - RESTE ACTIF (porte les equipes des 3 entreprises)</t>
+    <t>Fiches employes - RESTE ACTIF (3 entreprises)</t>
   </si>
   <si>
     <t>MOD_RH_ACTIVATE</t>
@@ -603,7 +609,7 @@
     <t>hr_holidays</t>
   </si>
   <si>
-    <t>Demandes de conges - RESTE ACTIF</t>
+    <t>Conges - RESTE ACTIF</t>
   </si>
   <si>
     <t>MOD_CONGES_ACTIVATE</t>
@@ -633,7 +639,7 @@
     <t>hr_recruitment</t>
   </si>
   <si>
-    <t>Pipeline de recrutement - RESTE ACTIF</t>
+    <t>Recrutement - RESTE ACTIF</t>
   </si>
   <si>
     <t>MOD_RECRUTEMENT_ACTIVATE</t>
@@ -807,10 +813,10 @@
     <t>MOD_RECYCLAGE_DEACTIVATE</t>
   </si>
   <si>
-    <t>20 modules Enterprise (payants, verifies 'uninstallable' sur ce serveur Community) exclus de ce catalogue - voir feuille 'Avantages licence Enterprise' pour leur valeur reelle.</t>
-  </si>
-  <si>
-    <t>Les 13 operations d'exploitation, faÃ§on BMC Control-M</t>
+    <t>20 modules Enterprise (payants, verifies 'uninstallable' sur ce serveur) exclus - voir feuille 'Avantages licence Enterprise'.</t>
+  </si>
+  <si>
+    <t>Les 13 operations d'exploitation, facon BMC Control-M</t>
   </si>
   <si>
     <t>Action Control-M</t>
@@ -942,7 +948,7 @@
     <t>Chaque action exige une raison et retape le JOB_ID en confirmation (discipline d'audit) - aucune derogation manuelle silencieuse.</t>
   </si>
   <si>
-    <t>Reference complete des jobs (source : jobs_table.csv, generee automatiquement)</t>
+    <t>Reference complete des jobs (genere depuis jobs_table.csv)</t>
   </si>
   <si>
     <t>JOB_ID</t>
@@ -2367,9 +2373,6 @@
     <t>Illustrations personnalisees - CLIM AUTO, COUL, PAIN &amp; GLACE</t>
   </si>
   <si>
-    <t>CLIM AUTO</t>
-  </si>
-  <si>
     <t>Garage / atelier climatisation automobile, Cocody, Abidjan</t>
   </si>
   <si>
@@ -2397,13 +2400,10 @@
     <t>1 demande de conges, 1 offre + candidat mecanicien - ILL_CLIMAUTO_CONGES / ILL_CLIMAUTO_RECRUTEMENT</t>
   </si>
   <si>
-    <t>Facture reelle envoyee par email</t>
-  </si>
-  <si>
-    <t>Revision + compresseur + gaz + main d'oeuvre (285 000 F CFA), postee et envoyee a contact@ankrr.fr - ILL_CLIMAUTO_FACTURE_MAIL</t>
-  </si>
-  <si>
-    <t>COUL</t>
+    <t>Facture reelle (PDF + email)</t>
+  </si>
+  <si>
+    <t>285 000 F CFA, PDF genere par wkhtmltopdf (identique a une facture Orange/MTN), envoyee a contact@ankrr.fr - ILL_CLIMAUTO_FACTURE_MAIL</t>
   </si>
   <si>
     <t>Parfumerie, Le Plateau, Abidjan</t>
@@ -2421,13 +2421,10 @@
     <t>Commande grossiste 200 flacons, compte pro salon coiffure, coffret entreprise, vente parfum (gagnee) - ILL_COUL_CRM_PISTES</t>
   </si>
   <si>
-    <t>3 parfums femme + 2 parfums homme + coffret cadeau (184 000 F CFA) - ILL_COUL_FACTURE_MAIL</t>
-  </si>
-  <si>
-    <t>PAIN &amp; GLACE</t>
-  </si>
-  <si>
-    <t>Boulangerie-glacier, Yopougon, Abidjan - prospect reel dont le comptable tient stock+compta sur Excel</t>
+    <t>184 000 F CFA - ILL_COUL_FACTURE_MAIL</t>
+  </si>
+  <si>
+    <t>Boulangerie-glacier, Yopougon - prospect reel dont le comptable tient stock+compta sur Excel</t>
   </si>
   <si>
     <t>res.company reelle - ILL_BOULANGERIE_SOCIETE</t>
@@ -2436,31 +2433,22 @@
     <t>Stock (6 references)</t>
   </si>
   <si>
-    <t>Baguette, croissant, pain de mie, 2 glaces, sorbet - quantites reelles, remplace directement le suivi Excel - ILL_BOULANGERIE_STOCK</t>
-  </si>
-  <si>
-    <t>Commande grossiste hotel (baguettes + croissants + glace vanille, 91 000 F CFA) - ILL_BOULANGERIE_FACTURE_MAIL</t>
-  </si>
-  <si>
-    <t>MECANISME REEL D'ENVOI</t>
-  </si>
-  <si>
-    <t>Les 3 factures utilisent le vrai moteur email d'Odoo (account.email_template_edi_invoice + ir.mail_server reel OVH) - PDF genere par wkhtmltopdf, envoye a contact@ankrr.fr. Voir feuille Securite pour l'incident reel rencontre (rejet OVH) et sa correction.</t>
-  </si>
-  <si>
-    <t>REGLE IMPORTANTE (donnees permanentes)</t>
-  </si>
-  <si>
-    <t>Desinstaller un module Odoo supprime REELLEMENT ses tables SQL - mail, hr, crm, account, stock, hr_holidays, hr_recruitment restent donc actifs en PERMANENCE (voir MOD_ALL_CLEANUP_FINAL.sh) pour ne jamais perdre ce travail d'illustration.</t>
-  </si>
-  <si>
-    <t>Ce que gagne PAIN &amp; GLACE (et tout client similaire) avec la licence Enterprise</t>
-  </si>
-  <si>
-    <t>Deja vu en Community (gratuit)</t>
-  </si>
-  <si>
-    <t>Stock (6 references PAIN &amp; GLACE, remplace Excel) + Comptabilite (facture reelle envoyee par email)</t>
+    <t>Baguette, croissant, pain de mie, 2 glaces, sorbet - remplace directement le suivi Excel - ILL_BOULANGERIE_STOCK</t>
+  </si>
+  <si>
+    <t>91 000 F CFA (commande grossiste hotel) - ILL_BOULANGERIE_FACTURE_MAIL</t>
+  </si>
+  <si>
+    <t>Les 3 factures utilisent le vrai moteur Odoo (account.email_template_edi_invoice + ir.mail_server OVH reel + wkhtmltopdf pour le PDF) - jamais une simulation. Voir feuille Securite pour les 2 incidents reels rencontres (rejet OVH, wkhtmltopdf invisible pour l'utilisateur odoo) et leurs corrections.</t>
+  </si>
+  <si>
+    <t>Desinstaller un module Odoo supprime REELLEMENT ses tables SQL - mail, hr, crm, account, stock, hr_holidays, hr_recruitment restent actifs en PERMANENCE (MOD_ALL_CLEANUP_FINAL.sh) pour ne jamais perdre ce travail.</t>
+  </si>
+  <si>
+    <t>Ce que gagne PAIN &amp; GLACE avec la licence Enterprise</t>
+  </si>
+  <si>
+    <t>Deja vu en Community (gratuit) : Stock (6 references, remplace Excel) + Comptabilite (facture PDF envoyee par email)</t>
   </si>
   <si>
     <t>Module Enterprise</t>
@@ -2472,7 +2460,7 @@
     <t>Pourquoi ca compte pour PAIN &amp; GLACE</t>
   </si>
   <si>
-    <t>accountant (Comptabilite complete)</t>
+    <t>accountant</t>
   </si>
   <si>
     <t>Rapprochement bancaire automatise, liasse fiscale, tableaux de bord financiers</t>
@@ -2481,7 +2469,7 @@
     <t>Le comptable ne ressaisit plus les releves bancaires a la main</t>
   </si>
   <si>
-    <t>stock_barcode (Codes-barres)</t>
+    <t>stock_barcode</t>
   </si>
   <si>
     <t>Inventaire au scanner, mouvements en 2 secondes</t>
@@ -2490,7 +2478,7 @@
     <t>Comptage physique du stock sans ressaisie papier vers Excel</t>
   </si>
   <si>
-    <t>web_mobile (App Android/iPhone)</t>
+    <t>web_mobile</t>
   </si>
   <si>
     <t>Application native, utilisable au comptoir, hors ligne</t>
@@ -2499,7 +2487,7 @@
     <t>Consultation du stock ou saisie d'une vente depuis le telephone</t>
   </si>
   <si>
-    <t>planning (Planification)</t>
+    <t>planning</t>
   </si>
   <si>
     <t>Plannings du personnel visibles par tous</t>
@@ -2508,16 +2496,16 @@
     <t>Remplace le planning papier affiche en cuisine</t>
   </si>
   <si>
-    <t>sign (Signature electronique)</t>
-  </si>
-  <si>
-    <t>Signature de documents a distance</t>
+    <t>sign</t>
+  </si>
+  <si>
+    <t>Signature electronique de documents a distance</t>
   </si>
   <si>
     <t>Contrats fournisseurs (farine, lait) sans imprimer/scanner</t>
   </si>
   <si>
-    <t>appointment (RDV en ligne)</t>
+    <t>appointment</t>
   </si>
   <si>
     <t>Reservation en ligne</t>
@@ -2526,7 +2514,7 @@
     <t>Commande de gateau sur mesure sans appel telephonique</t>
   </si>
   <si>
-    <t>knowledge (Base de connaissances)</t>
+    <t>knowledge</t>
   </si>
   <si>
     <t>Recettes et procedures centralisees</t>
@@ -2535,7 +2523,7 @@
     <t>Remplace les recettes sur cahier ou fichiers eparpilles</t>
   </si>
   <si>
-    <t>quality_control (Controle qualite)</t>
+    <t>quality_control</t>
   </si>
   <si>
     <t>Points de controle traces (temperature, DLC)</t>
@@ -2544,7 +2532,7 @@
     <t>Tracabilite alimentaire reelle, utile en cas de controle sanitaire</t>
   </si>
   <si>
-    <t>timesheet_grid (Feuilles de temps)</t>
+    <t>timesheet_grid</t>
   </si>
   <si>
     <t>Heures reellement travaillees, liees a la paie</t>
@@ -2562,7 +2550,7 @@
     <t>Fidelisation sans y penser chaque semaine</t>
   </si>
   <si>
-    <t>HONNETETE DU PROJET : le Community couvre deja l'essentiel demontre ici. L'Enterprise se justifie quand la douleur devient reelle et chiffrable (rapprochement bancaire manuel, ressaisie stock, paie a la main) - faire raconter cette douleur au client avant de proposer l'abonnement, jamais l'ordre inverse. Detail complet : docs/AVANTAGES_LICENCE_ENTERPRISE.md</t>
+    <t>HONNETETE : le Community couvre deja l'essentiel demontre ici. L'Enterprise se justifie quand la douleur devient reelle et chiffrable - faire raconter cette douleur au client avant de proposer l'abonnement, jamais l'ordre inverse.</t>
   </si>
   <si>
     <t>Vocabulaire - correspondance avec Control-M</t>
@@ -2589,13 +2577,13 @@
     <t>OUT-condition</t>
   </si>
   <si>
-    <t>Colonne OUT_COND - marque un fichier .ok dans state/ une fois le job reussi</t>
+    <t>Colonne OUT_COND - marque un fichier .ok une fois le job reussi</t>
   </si>
   <si>
     <t>AJP / Plan du jour</t>
   </si>
   <si>
-    <t>jobs_table.csv + l'etat courant dans state/ (pas de notion de 'jour' - continu)</t>
+    <t>jobs_table.csv + l'etat courant dans state/</t>
   </si>
   <si>
     <t>Force Start</t>
@@ -2655,7 +2643,7 @@
     <t>Discipline des secrets</t>
   </si>
   <si>
-    <t>AUCUN mot de passe reel dans vars.conf ni dans aucun fichier versionne sur GitHub - toujours secrets/*.txt, chmod 600, exclu par .gitignore</t>
+    <t>AUCUN mot de passe dans vars.conf ni GitHub - toujours secrets/*.txt, chmod 600, exclu par .gitignore</t>
   </si>
   <si>
     <t>Deposer le mot de passe SMTP</t>
@@ -2667,13 +2655,13 @@
     <t>Alertes email (echecs de job)</t>
   </si>
   <si>
-    <t>Actives - envoyees par orchestrator.sh a CHAQUE echec reel, objet [ERP_CRM_FACTORY]</t>
+    <t>Actives - envoyees a CHAQUE echec reel, objet [ERP_CRM_FACTORY]</t>
   </si>
   <si>
     <t>Email sortant Odoo (factures)</t>
   </si>
   <si>
-    <t>Configure sur le vrai relais OVH (ODOO_MAIL_SERVER_REAL) - ir.mail_server + mail.alias.domain</t>
+    <t>Relais OVH reel - ir.mail_server + mail.alias.domain</t>
   </si>
   <si>
     <t>Tester la config alertes</t>
@@ -2682,41 +2670,50 @@
     <t>./notifier.sh --test</t>
   </si>
   <si>
-    <t>INCIDENT REEL DU 2026-09-01 (rejet OVH des factures)</t>
-  </si>
-  <si>
-    <t>Constat : OVH a renvoye 'Rejected by policy: From header domain does not align with authenticated domain'. Cause reelle (lue dans le code source Odoo, jamais supposee) : Odoo utilisait son repli code en dur 'OdooBot &lt;odoobot@example.com&gt;' comme expediteur, car aucune societe n'avait de mail.alias.domain configure. OVH exige que le domaine du From corresponde exactement au compte authentifie (contact@ankrr.fr) - politique anti-usurpation standard. Corrige a la racine (ODOO_MAIL_SERVER_REAL.sh) : mail.alias.domain='ankrr.fr' + default_from='contact', applique a TOUTES les societes - plus aucun email sortant ne peut retomber sur odoobot@example.com.</t>
+    <t>OVH a rejete : 'From header domain does not align with authenticated domain'. Cause reelle : aucune societe n'avait de mail.alias.domain configure, Odoo retombait sur 'OdooBot &lt;odoobot@example.com&gt;'. Corrige a la racine (ODOO_MAIL_SERVER_REAL.sh) pour toutes les societes, presentes et futures.</t>
+  </si>
+  <si>
+    <t>Unable to find Wkhtmltopdf' - le paquet installe ses binaires dans /usr/local/bin, absent du PATH de l'utilisateur odoo (meme piege que Python 3.11 plus tot). Corrige par lien symbolique vers /usr/bin + verification explicite du point de vue de l'utilisateur odoo, jamais seulement root.</t>
   </si>
   <si>
     <t>INCIDENT REEL - entrepot manquant</t>
   </si>
   <si>
-    <t>Une societe creee avant l'activation du module Stock n'a pas d'entrepot par defaut - cree explicitement dans ILL_BOULANGERIE_STOCK.sh (meme schema qu'Odoo utilise en interne).</t>
+    <t>Une societe creee avant l'activation du module Stock n'a pas d'entrepot par defaut - cree explicitement (ILL_BOULANGERIE_STOCK.sh).</t>
   </si>
   <si>
     <t>INCIDENT REEL - plan comptable manquant</t>
   </si>
   <si>
-    <t>Une societe multi-entreprise n'a aucun journal comptable tant qu'un plan comptable ne lui est pas charge - env['account.chart.template'].try_loading('generic_coa', company) ajoute dans chaque job de facturation.</t>
+    <t>Une societe multi-entreprise n'a aucun journal comptable sans chargement explicite - account.chart.template.try_loading('generic_coa', company).</t>
+  </si>
+  <si>
+    <t>INCIDENT REEL - ES_021 (WAZ_ELK_FACTORY)</t>
+  </si>
+  <si>
+    <t>Une etudiante deployant depuis GitHub a rencontre un echec reel sur le keystore Elasticsearch (execute en root au lieu de l'utilisateur elasticsearch) - corrige, meme famille de lecon que le PDF ci-dessus.</t>
+  </si>
+  <si>
+    <t>Deploiement verifie depuis GitHub (2026-09-02)</t>
+  </si>
+  <si>
+    <t>git clone reel sur la VM + orchestrateur complet -&gt; TERMINE SANS ECHEC, une fois le mot de passe SMTP correctement depose.</t>
   </si>
   <si>
     <t>Comptes de la demo</t>
   </si>
   <si>
-    <t>Connexion web : admin/admin (a changer avant une vraie presentation client). Mot de passe maitre et PostgreSQL generes aleatoirement, stockes uniquement dans secrets/ sur la VM.</t>
-  </si>
-  <si>
-    <t>Lecon transversale du 2026-09-01</t>
-  </si>
-  <si>
-    <t>Un chemin RELATIF donne a un operateur est une source d'erreur reelle - toujours un chemin ABSOLU depuis le home (~/erp_crm_factory/...). Une reponse 'accepte par le serveur SMTP' n'est PAS une preuve de livraison reelle - le rejet peut arriver de facon asynchrone (bounce) apres coup ; verifier la boite de reception reelle reste la seule preuve definitive.</t>
+    <t>Connexion web : admin/admin (a changer avant une vraie presentation client). Mots de passe generes aleatoirement, stockes uniquement dans secrets/ sur la VM.</t>
+  </si>
+  <si>
+    <t>Une reponse 'accepte par le serveur' n'est PAS une preuve de livraison reelle (bounce asynchrone possible). Une verification faite en root ne prouve rien pour l'utilisateur reel d'execution. Toujours verifier du point de vue exact de qui/quoi va reellement s'en servir.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2733,22 +2730,37 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="14"/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Consolas"/>
       <family val="3"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FF1F4E78"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -2781,7 +2793,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -2789,34 +2801,99 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3132,194 +3209,208 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA8BED1F-804A-46D2-B7E2-F5C0C831B1F9}">
-  <dimension ref="A1:B26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C79D639-1DB1-45DE-8B56-A9F2061B2AC0}">
+  <dimension ref="A1:B29"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.77734375" customWidth="1"/>
-    <col min="2" max="2" width="90.77734375" customWidth="1"/>
+    <col min="1" max="1" width="30.77734375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="95.77734375" style="1" customWidth="1"/>
+    <col min="3" max="16384" width="11.5546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:2" ht="19.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
+      <c r="B1" s="16"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="1" t="s">
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+      <c r="B9" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="1" t="s">
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
+      <c r="B10" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="1" t="s">
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
+      <c r="B11" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="1" t="s">
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
+      <c r="B12" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="1" t="s">
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
+      <c r="B13" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="1" t="s">
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="1" t="s">
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="B15" s="3" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="1" t="s">
+      <c r="A17" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
+    <row r="18" spans="1:2" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="1" t="s">
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B21" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B22" s="3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B23" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B24" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B25" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B26" s="3" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B27" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B28" s="3" t="s">
         <v>44</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -3332,98 +3423,117 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EE59217-FAAA-43C8-B601-CC336B4BB36C}">
-  <dimension ref="A1:B16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05191313-14B0-447E-BD46-3C7B7DFA2CB8}">
+  <dimension ref="A1:B21"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.77734375" customWidth="1"/>
-    <col min="2" max="2" width="70.77734375" customWidth="1"/>
+    <col min="1" max="1" width="32.77734375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="75.77734375" style="1" customWidth="1"/>
+    <col min="3" max="16384" width="11.5546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="16" t="s">
+        <v>864</v>
+      </c>
+      <c r="B1" s="16"/>
+    </row>
+    <row r="2" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="21" t="s">
+        <v>865</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="12" t="s">
+        <v>867</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>868</v>
       </c>
-      <c r="B1" s="7"/>
-    </row>
-    <row r="2" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="21" t="s">
         <v>869</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B5" s="21" t="s">
         <v>870</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="13" t="s">
         <v>871</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B6" s="13" t="s">
         <v>872</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="12" t="s">
         <v>873</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B7" s="8" t="s">
         <v>874</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+    <row r="9" spans="1:2" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="19"/>
+      <c r="B9" s="6" t="s">
         <v>875</v>
       </c>
-      <c r="B6" s="1" t="s">
+    </row>
+    <row r="11" spans="1:2" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A11" s="19"/>
+      <c r="B11" s="22" t="s">
         <v>876</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+    <row r="13" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="21" t="s">
         <v>877</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B13" s="21" t="s">
         <v>878</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+    <row r="14" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="13" t="s">
         <v>879</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B14" s="13" t="s">
         <v>880</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
+    <row r="15" spans="1:2" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A15" s="12" t="s">
         <v>881</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B15" s="12" t="s">
         <v>882</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
+    <row r="17" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="6" t="s">
         <v>883</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B17" s="6" t="s">
         <v>884</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
+    <row r="19" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="6" t="s">
         <v>885</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B19" s="6" t="s">
         <v>886</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="72" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
+    <row r="21" spans="1:2" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A21" s="19"/>
+      <c r="B21" s="6" t="s">
         <v>887</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>888</v>
       </c>
     </row>
   </sheetData>
@@ -3435,204 +3545,207 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FFF15F7-B440-4A78-8C90-D55E263315D5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22C8293E-BE72-48F6-97EF-59B74045AB31}">
   <dimension ref="A1:A13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="100.77734375" customWidth="1"/>
+    <col min="1" max="1" width="105.77734375" style="1" customWidth="1"/>
+    <col min="2" max="16384" width="11.5546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
-        <v>27</v>
+    <row r="1" spans="1:1" ht="19.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
-        <v>45</v>
+      <c r="A2" s="7" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
-        <v>46</v>
+      <c r="A3" s="9" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
-        <v>48</v>
+      <c r="A4" s="9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="9" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
+      <c r="A6" s="9" t="s">
         <v>51</v>
       </c>
     </row>
+    <row r="7" spans="1:1" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="9" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
-        <v>53</v>
+      <c r="A9" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="9" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="5" t="s">
-        <v>55</v>
+      <c r="A11" s="8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="10" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39E80B44-E9C2-441F-AB0C-062B7B261655}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2597BBDA-1BAD-4E8E-A9A9-9D5CFA8730F9}">
   <dimension ref="A1:A27"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="100.77734375" customWidth="1"/>
+    <col min="1" max="1" width="105.77734375" style="1" customWidth="1"/>
+    <col min="2" max="16384" width="11.5546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
-        <v>56</v>
+    <row r="1" spans="1:1" ht="19.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>57</v>
+      <c r="A2" s="6" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>58</v>
+      <c r="A4" s="4" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
-        <v>59</v>
+      <c r="A5" s="7" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
-        <v>60</v>
+      <c r="A6" s="9" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
-        <v>61</v>
+      <c r="A7" s="9" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="9" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="9" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" s="8" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="9" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="8" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>71</v>
+      <c r="A21" s="4" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" s="4" t="s">
-        <v>72</v>
+      <c r="A22" s="7" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" s="4" t="s">
-        <v>73</v>
+      <c r="A23" s="9" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24" s="4" t="s">
-        <v>74</v>
+      <c r="A24" s="9" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25" s="4" t="s">
-        <v>75</v>
+      <c r="A25" s="9" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A26" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A27" s="4" t="s">
-        <v>77</v>
+      <c r="A26" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" s="8" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -3641,628 +3754,629 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCB49944-5B0C-4444-A63B-ED00F5B544C0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FECBAB7-D966-47C4-8270-781C806EA7B5}">
   <dimension ref="A1:E37"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.77734375" customWidth="1"/>
-    <col min="2" max="2" width="22.77734375" customWidth="1"/>
-    <col min="3" max="3" width="50.77734375" customWidth="1"/>
-    <col min="4" max="5" width="18.77734375" customWidth="1"/>
+    <col min="1" max="1" width="16.77734375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="24.77734375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="55.77734375" style="1" customWidth="1"/>
+    <col min="4" max="5" width="20.77734375" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="11.5546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-    </row>
-    <row r="2" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="B2" s="6" t="s">
+    <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="B2" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="C2" s="11" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="D2" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="E2" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="1" t="s">
+    </row>
+    <row r="3" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="B3" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="C3" s="13" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="D3" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="E3" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="C4" s="1" t="s">
+    </row>
+    <row r="4" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="B4" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="C4" s="13" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+      <c r="D4" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="E4" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="C5" s="1" t="s">
+    </row>
+    <row r="5" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="B5" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="C5" s="13" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+      <c r="D5" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="E5" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="C6" s="1" t="s">
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="B6" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="C6" s="13" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+      <c r="D6" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="E6" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="C7" s="1" t="s">
+    </row>
+    <row r="7" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="B7" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="C7" s="13" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+      <c r="D7" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="E7" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="C8" s="1" t="s">
+    </row>
+    <row r="8" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="B8" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="C8" s="13" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+      <c r="D8" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="E8" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="C9" s="1" t="s">
+    </row>
+    <row r="9" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A9" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="B9" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="C9" s="13" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
+      <c r="D9" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="E9" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="C10" s="1" t="s">
+    </row>
+    <row r="10" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A10" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="B10" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="C10" s="13" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
+      <c r="D10" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="E10" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="C11" s="1" t="s">
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="B11" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="C11" s="13" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
+      <c r="D11" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="E11" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="C12" s="1" t="s">
+    </row>
+    <row r="12" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A12" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="B12" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="C12" s="13" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
+      <c r="D12" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="E12" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="C13" s="1" t="s">
+    </row>
+    <row r="13" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A13" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="B13" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="C13" s="13" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
+      <c r="D13" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="E13" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="C14" s="1" t="s">
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="B14" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="C14" s="13" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
+      <c r="D14" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="E14" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="C15" s="1" t="s">
+    </row>
+    <row r="15" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A15" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="B15" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="C15" s="13" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
+      <c r="D15" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="E15" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="C16" s="1" t="s">
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="B16" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="C16" s="13" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
+      <c r="D16" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="E16" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="C17" s="1" t="s">
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="B17" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="C17" s="13" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
+      <c r="D17" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="E17" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="C18" s="1" t="s">
+    </row>
+    <row r="18" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A18" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="B18" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="C18" s="13" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
+      <c r="D18" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="E18" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="C19" s="1" t="s">
+    </row>
+    <row r="19" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A19" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="B19" s="13" t="s">
         <v>167</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="C19" s="13" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
+      <c r="D19" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="E19" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="C20" s="1" t="s">
+    </row>
+    <row r="20" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A20" s="13" t="s">
         <v>171</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="B20" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="C20" s="13" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
+      <c r="D20" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="E20" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="C21" s="1" t="s">
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="B21" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="C21" s="13" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
+      <c r="D21" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="E21" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="C22" s="1" t="s">
+    </row>
+    <row r="22" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A22" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="B22" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="C22" s="13" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
+      <c r="D22" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="E22" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="C23" s="1" t="s">
+    </row>
+    <row r="23" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A23" s="13" t="s">
         <v>186</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="B23" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="C23" s="13" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
+      <c r="D23" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="E23" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="C24" s="1" t="s">
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="13" t="s">
         <v>191</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="B24" s="13" t="s">
         <v>192</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="C24" s="13" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
+      <c r="D24" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="E24" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="C25" s="1" t="s">
+    </row>
+    <row r="25" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A25" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="B25" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="C25" s="13" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
+      <c r="D25" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="E25" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="C26" s="1" t="s">
+    </row>
+    <row r="26" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A26" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="B26" s="13" t="s">
         <v>202</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="C26" s="13" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A27" s="1" t="s">
+      <c r="D26" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="E26" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="C27" s="1" t="s">
+    </row>
+    <row r="27" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A27" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="B27" s="13" t="s">
         <v>207</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="C27" s="13" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="1" t="s">
+      <c r="D27" s="9" t="s">
         <v>209</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="E27" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="C28" s="1" t="s">
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="13" t="s">
         <v>211</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="B28" s="13" t="s">
         <v>212</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="C28" s="13" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
+      <c r="D28" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="E28" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="C29" s="1" t="s">
+    </row>
+    <row r="29" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A29" s="13" t="s">
         <v>216</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="B29" s="13" t="s">
         <v>217</v>
       </c>
-      <c r="E29" s="4" t="s">
+      <c r="C29" s="13" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A30" s="1" t="s">
+      <c r="D29" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="E29" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="C30" s="1" t="s">
+    </row>
+    <row r="30" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A30" s="13" t="s">
         <v>221</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="B30" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="E30" s="4" t="s">
+      <c r="C30" s="13" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A31" s="1" t="s">
+      <c r="D30" s="9" t="s">
         <v>224</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="E30" s="9" t="s">
         <v>225</v>
       </c>
-      <c r="C31" s="1" t="s">
+    </row>
+    <row r="31" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A31" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="B31" s="13" t="s">
         <v>227</v>
       </c>
-      <c r="E31" s="4" t="s">
+      <c r="C31" s="13" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A32" s="1" t="s">
+      <c r="D31" s="9" t="s">
         <v>229</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="E31" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="C32" s="1" t="s">
+    </row>
+    <row r="32" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A32" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="B32" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="C32" s="13" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
+      <c r="D32" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="E32" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="C33" s="1" t="s">
+    </row>
+    <row r="33" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A33" s="13" t="s">
         <v>236</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="B33" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="E33" s="4" t="s">
+      <c r="C33" s="13" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A34" s="1" t="s">
+      <c r="D33" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="E33" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="C34" s="1" t="s">
+    </row>
+    <row r="34" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A34" s="13" t="s">
         <v>241</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="B34" s="13" t="s">
         <v>242</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="C34" s="13" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A35" s="1" t="s">
+      <c r="D34" s="9" t="s">
         <v>244</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="E34" s="9" t="s">
         <v>245</v>
       </c>
-      <c r="C35" s="1" t="s">
+    </row>
+    <row r="35" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A35" s="13" t="s">
         <v>246</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="B35" s="13" t="s">
         <v>247</v>
       </c>
-      <c r="E35" s="4" t="s">
+      <c r="C35" s="13" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A36" s="1" t="s">
+      <c r="D35" s="9" t="s">
         <v>249</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="E35" s="9" t="s">
         <v>250</v>
       </c>
-      <c r="C36" s="1" t="s">
+    </row>
+    <row r="36" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A36" s="13" t="s">
         <v>251</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="B36" s="13" t="s">
         <v>252</v>
       </c>
-      <c r="E36" s="4" t="s">
+      <c r="C36" s="13" t="s">
         <v>253</v>
       </c>
+      <c r="D36" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>255</v>
+      </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37" s="8" t="s">
-        <v>254</v>
-      </c>
-      <c r="B37" s="8"/>
-      <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
+      <c r="A37" s="17" t="s">
+        <v>256</v>
+      </c>
+      <c r="B37" s="17"/>
+      <c r="C37" s="17"/>
+      <c r="D37" s="17"/>
+      <c r="E37" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4275,182 +4389,183 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{740EF00B-869A-4721-8D9F-146B18857963}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCC9A788-EA16-4583-AEEA-47ABC0A49478}">
   <dimension ref="A1:C17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.77734375" customWidth="1"/>
-    <col min="2" max="2" width="55.77734375" customWidth="1"/>
-    <col min="3" max="3" width="50.77734375" customWidth="1"/>
+    <col min="1" max="1" width="24.77734375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="58.77734375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="52.77734375" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="11.5546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-    </row>
-    <row r="2" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="B2" s="6" t="s">
+    <row r="1" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="16" t="s">
         <v>257</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="11" t="s">
         <v>258</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="B2" s="11" t="s">
         <v>259</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C2" s="11" t="s">
         <v>260</v>
       </c>
-      <c r="C3" s="4" t="s">
+    </row>
+    <row r="3" spans="1:3" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="15" t="s">
         <v>261</v>
       </c>
+      <c r="B3" s="13" t="s">
+        <v>262</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>263</v>
+      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="C4" s="4" t="s">
+      <c r="A4" s="15" t="s">
         <v>264</v>
       </c>
+      <c r="B4" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>266</v>
+      </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="C5" s="4" t="s">
+      <c r="A5" s="15" t="s">
         <v>267</v>
       </c>
+      <c r="B5" s="13" t="s">
+        <v>268</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="C6" s="4" t="s">
+      <c r="A6" s="15" t="s">
         <v>270</v>
       </c>
+      <c r="B6" s="13" t="s">
+        <v>271</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="C7" s="4" t="s">
+      <c r="A7" s="15" t="s">
         <v>273</v>
       </c>
+      <c r="B7" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>275</v>
+      </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="C8" s="4" t="s">
+      <c r="A8" s="15" t="s">
         <v>276</v>
       </c>
+      <c r="B8" s="13" t="s">
+        <v>277</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>278</v>
+      </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="C9" s="4" t="s">
+      <c r="A9" s="15" t="s">
         <v>279</v>
       </c>
+      <c r="B9" s="13" t="s">
+        <v>280</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>281</v>
+      </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="C10" s="4" t="s">
+      <c r="A10" s="15" t="s">
         <v>282</v>
       </c>
+      <c r="B10" s="13" t="s">
+        <v>283</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>284</v>
+      </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="C11" s="4" t="s">
+      <c r="A11" s="15" t="s">
         <v>285</v>
       </c>
+      <c r="B11" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="C12" s="4" t="s">
+      <c r="A12" s="15" t="s">
         <v>288</v>
       </c>
+      <c r="B12" s="13" t="s">
+        <v>289</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>290</v>
+      </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="C13" s="4" t="s">
+      <c r="A13" s="15" t="s">
         <v>291</v>
       </c>
+      <c r="B13" s="13" t="s">
+        <v>292</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>293</v>
+      </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="C14" s="4" t="s">
+      <c r="A14" s="15" t="s">
         <v>294</v>
       </c>
+      <c r="B14" s="13" t="s">
+        <v>295</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>296</v>
+      </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="C15" s="4" t="s">
+      <c r="A15" s="14" t="s">
         <v>297</v>
       </c>
+      <c r="B15" s="12" t="s">
+        <v>298</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>299</v>
+      </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
-        <v>298</v>
-      </c>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
+      <c r="A17" s="18" t="s">
+        <v>300</v>
+      </c>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4462,2759 +4577,2760 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6C90DF5-FA46-4358-9031-856306C251F1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E2CEDD9-E31F-4AF3-B375-9FBAAFE809BB}">
   <dimension ref="A1:H106"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.77734375" customWidth="1"/>
-    <col min="2" max="2" width="30.77734375" customWidth="1"/>
-    <col min="3" max="3" width="14.77734375" customWidth="1"/>
-    <col min="4" max="4" width="10.77734375" customWidth="1"/>
-    <col min="5" max="5" width="32.77734375" customWidth="1"/>
-    <col min="6" max="6" width="55.77734375" customWidth="1"/>
-    <col min="7" max="8" width="26.77734375" customWidth="1"/>
+    <col min="1" max="1" width="30.77734375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.77734375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.77734375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.77734375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="34.77734375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="58.77734375" style="1" customWidth="1"/>
+    <col min="7" max="8" width="28.77734375" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="11.5546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-    </row>
-    <row r="2" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
-        <v>300</v>
-      </c>
-      <c r="B2" s="6" t="s">
+    <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="16" t="s">
         <v>301</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="11" t="s">
         <v>302</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="B2" s="11" t="s">
         <v>303</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="C2" s="11" t="s">
         <v>304</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="D2" s="11" t="s">
         <v>305</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="E2" s="11" t="s">
         <v>306</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="F2" s="11" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+      <c r="G2" s="11" t="s">
         <v>308</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="H2" s="11" t="s">
         <v>309</v>
       </c>
-      <c r="C3" s="1" t="s">
+    </row>
+    <row r="3" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="9" t="s">
         <v>310</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="B3" s="13" t="s">
         <v>311</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="G3" s="1" t="s">
+      <c r="C3" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E3" s="9" t="s">
         <v>314</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="F3" s="13" t="s">
         <v>315</v>
       </c>
+      <c r="G3" s="13" t="s">
+        <v>316</v>
+      </c>
+      <c r="H3" s="13" t="s">
+        <v>317</v>
+      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="B4" s="1" t="s">
+      <c r="A4" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>319</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="G4" s="13" t="s">
         <v>317</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>320</v>
+      <c r="H4" s="13" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="B5" s="1" t="s">
+      <c r="A5" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>324</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>326</v>
+      </c>
+      <c r="G5" s="13" t="s">
         <v>322</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="B6" s="1" t="s">
+      <c r="H5" s="13" t="s">
         <v>327</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E6" s="4" t="s">
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
         <v>328</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="B6" s="13" t="s">
         <v>329</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="H6" s="1" t="s">
+      <c r="C6" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E6" s="9" t="s">
         <v>330</v>
       </c>
+      <c r="F6" s="13" t="s">
+        <v>331</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>327</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>332</v>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
-        <v>331</v>
-      </c>
-      <c r="B7" s="1" t="s">
+      <c r="A7" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>334</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>336</v>
+      </c>
+      <c r="G7" s="13" t="s">
         <v>332</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>333</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
-        <v>336</v>
-      </c>
-      <c r="B8" s="1" t="s">
+      <c r="H7" s="13" t="s">
         <v>337</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E8" s="4" t="s">
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="9" t="s">
         <v>338</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="B8" s="13" t="s">
         <v>339</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="H8" s="1" t="s">
+      <c r="C8" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E8" s="9" t="s">
         <v>340</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
+      <c r="F8" s="13" t="s">
         <v>341</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="G8" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="H8" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E9" s="4" t="s">
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="9" t="s">
         <v>343</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="B9" s="13" t="s">
         <v>344</v>
       </c>
-      <c r="G9" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="H9" s="1" t="s">
+      <c r="C9" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E9" s="9" t="s">
         <v>345</v>
       </c>
+      <c r="F9" s="13" t="s">
+        <v>346</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>342</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>347</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
-        <v>346</v>
-      </c>
-      <c r="B10" s="1" t="s">
+      <c r="A10" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>349</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>351</v>
+      </c>
+      <c r="G10" s="13" t="s">
         <v>347</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>350</v>
+      <c r="H10" s="13" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
-        <v>351</v>
-      </c>
-      <c r="B11" s="1" t="s">
+      <c r="A11" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>354</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>356</v>
+      </c>
+      <c r="G11" s="13" t="s">
         <v>352</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>353</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>355</v>
+      <c r="H11" s="13" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
-        <v>356</v>
-      </c>
-      <c r="B12" s="1" t="s">
+      <c r="A12" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>359</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>361</v>
+      </c>
+      <c r="G12" s="13" t="s">
         <v>357</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>358</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
-        <v>361</v>
-      </c>
-      <c r="B13" s="1" t="s">
+      <c r="H12" s="13" t="s">
         <v>362</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E13" s="4" t="s">
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="9" t="s">
         <v>363</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="B13" s="13" t="s">
         <v>364</v>
       </c>
-      <c r="G13" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="H13" s="1" t="s">
+      <c r="C13" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E13" s="9" t="s">
         <v>365</v>
       </c>
+      <c r="F13" s="13" t="s">
+        <v>366</v>
+      </c>
+      <c r="G13" s="13" t="s">
+        <v>362</v>
+      </c>
+      <c r="H13" s="13" t="s">
+        <v>367</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
-        <v>366</v>
-      </c>
-      <c r="B14" s="1" t="s">
+      <c r="A14" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>369</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>370</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>371</v>
+      </c>
+      <c r="G14" s="13" t="s">
         <v>367</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>368</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>370</v>
+      <c r="H14" s="13" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
-        <v>371</v>
-      </c>
-      <c r="B15" s="1" t="s">
+      <c r="A15" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>374</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>375</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="G15" s="13" t="s">
         <v>372</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>373</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>375</v>
+      <c r="H15" s="13" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
-        <v>376</v>
-      </c>
-      <c r="B16" s="1" t="s">
+      <c r="A16" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>379</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>380</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>381</v>
+      </c>
+      <c r="G16" s="13" t="s">
         <v>377</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>378</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>379</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>380</v>
+      <c r="H16" s="13" t="s">
+        <v>382</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
-        <v>381</v>
-      </c>
-      <c r="B17" s="1" t="s">
+      <c r="A17" s="9" t="s">
+        <v>383</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>384</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="F17" s="13" t="s">
+        <v>386</v>
+      </c>
+      <c r="G17" s="13" t="s">
         <v>382</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>383</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
-        <v>386</v>
-      </c>
-      <c r="B18" s="1" t="s">
+      <c r="H17" s="13" t="s">
         <v>387</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E18" s="4" t="s">
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="9" t="s">
         <v>388</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="B18" s="13" t="s">
         <v>389</v>
       </c>
-      <c r="G18" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="H18" s="1" t="s">
+      <c r="C18" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E18" s="9" t="s">
         <v>390</v>
       </c>
+      <c r="F18" s="13" t="s">
+        <v>391</v>
+      </c>
+      <c r="G18" s="13" t="s">
+        <v>387</v>
+      </c>
+      <c r="H18" s="13" t="s">
+        <v>392</v>
+      </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="4" t="s">
-        <v>391</v>
-      </c>
-      <c r="B19" s="1" t="s">
+      <c r="A19" s="9" t="s">
+        <v>393</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>394</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>395</v>
+      </c>
+      <c r="F19" s="13" t="s">
+        <v>396</v>
+      </c>
+      <c r="G19" s="13" t="s">
         <v>392</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>393</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>395</v>
+      <c r="H19" s="13" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="4" t="s">
-        <v>396</v>
-      </c>
-      <c r="B20" s="1" t="s">
+      <c r="A20" s="9" t="s">
+        <v>398</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>399</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>400</v>
+      </c>
+      <c r="F20" s="13" t="s">
+        <v>401</v>
+      </c>
+      <c r="G20" s="13" t="s">
         <v>397</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>398</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>400</v>
+      <c r="H20" s="13" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="4" t="s">
-        <v>401</v>
-      </c>
-      <c r="B21" s="1" t="s">
+      <c r="A21" s="9" t="s">
+        <v>403</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>404</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>405</v>
+      </c>
+      <c r="F21" s="13" t="s">
+        <v>406</v>
+      </c>
+      <c r="G21" s="13" t="s">
         <v>402</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>403</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>405</v>
+      <c r="H21" s="13" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="4" t="s">
-        <v>406</v>
-      </c>
-      <c r="B22" s="1" t="s">
+      <c r="A22" s="9" t="s">
+        <v>408</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>409</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>410</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>411</v>
+      </c>
+      <c r="G22" s="13" t="s">
         <v>407</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>408</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A23" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E23" s="4" t="s">
+      <c r="H22" s="13" t="s">
         <v>412</v>
       </c>
-      <c r="F23" s="1" t="s">
+    </row>
+    <row r="23" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A23" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="B23" s="13" t="s">
         <v>413</v>
       </c>
-      <c r="G23" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="H23" s="1" t="s">
+      <c r="C23" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E23" s="9" t="s">
         <v>414</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A24" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B24" s="1" t="s">
+      <c r="F23" s="13" t="s">
         <v>415</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E24" s="4" t="s">
+      <c r="G23" s="13" t="s">
+        <v>412</v>
+      </c>
+      <c r="H23" s="13" t="s">
         <v>416</v>
       </c>
-      <c r="F24" s="1" t="s">
+    </row>
+    <row r="24" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B24" s="13" t="s">
         <v>417</v>
       </c>
-      <c r="G24" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="H24" s="1" t="s">
+      <c r="C24" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E24" s="9" t="s">
         <v>418</v>
       </c>
+      <c r="F24" s="13" t="s">
+        <v>419</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>416</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>420</v>
+      </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>420</v>
-      </c>
-      <c r="F25" s="1" t="s">
+      <c r="A25" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B25" s="13" t="s">
         <v>421</v>
       </c>
-      <c r="G25" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="H25" s="1" t="s">
+      <c r="C25" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E25" s="9" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A26" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="B26" s="1" t="s">
+      <c r="F25" s="13" t="s">
         <v>423</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E26" s="4" t="s">
+      <c r="G25" s="13" t="s">
+        <v>412</v>
+      </c>
+      <c r="H25" s="13" t="s">
         <v>424</v>
       </c>
-      <c r="F26" s="1" t="s">
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="B26" s="13" t="s">
         <v>425</v>
       </c>
-      <c r="G26" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="H26" s="1" t="s">
+      <c r="C26" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E26" s="9" t="s">
         <v>426</v>
       </c>
+      <c r="F26" s="13" t="s">
+        <v>427</v>
+      </c>
+      <c r="G26" s="13" t="s">
+        <v>424</v>
+      </c>
+      <c r="H26" s="13" t="s">
+        <v>428</v>
+      </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>428</v>
-      </c>
-      <c r="F27" s="1" t="s">
+      <c r="A27" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="B27" s="13" t="s">
         <v>429</v>
       </c>
-      <c r="G27" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="H27" s="1" t="s">
+      <c r="C27" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E27" s="9" t="s">
         <v>430</v>
       </c>
+      <c r="F27" s="13" t="s">
+        <v>431</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>412</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>432</v>
+      </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E28" s="4" t="s">
+      <c r="A28" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>433</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>435</v>
+      </c>
+      <c r="G28" s="13" t="s">
         <v>432</v>
       </c>
-      <c r="F28" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A29" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E29" s="4" t="s">
+      <c r="H28" s="13" t="s">
         <v>436</v>
       </c>
-      <c r="F29" s="1" t="s">
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="B29" s="13" t="s">
         <v>437</v>
       </c>
-      <c r="G29" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="H29" s="1" t="s">
+      <c r="C29" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E29" s="9" t="s">
         <v>438</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A30" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="B30" s="1" t="s">
+      <c r="F29" s="13" t="s">
         <v>439</v>
       </c>
-      <c r="C30" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E30" s="4" t="s">
+      <c r="G29" s="13" t="s">
+        <v>412</v>
+      </c>
+      <c r="H29" s="13" t="s">
         <v>440</v>
       </c>
-      <c r="F30" s="1" t="s">
+    </row>
+    <row r="30" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A30" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="B30" s="13" t="s">
         <v>441</v>
       </c>
-      <c r="G30" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="H30" s="1" t="s">
+      <c r="C30" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E30" s="9" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A31" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="B31" s="1" t="s">
+      <c r="F30" s="13" t="s">
         <v>443</v>
       </c>
-      <c r="C31" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E31" s="4" t="s">
+      <c r="G30" s="13" t="s">
+        <v>440</v>
+      </c>
+      <c r="H30" s="13" t="s">
         <v>444</v>
       </c>
-      <c r="F31" s="1" t="s">
+    </row>
+    <row r="31" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A31" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="B31" s="13" t="s">
         <v>445</v>
       </c>
-      <c r="G31" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="H31" s="1" t="s">
+      <c r="C31" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E31" s="9" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A32" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="B32" s="1" t="s">
+      <c r="F31" s="13" t="s">
         <v>447</v>
       </c>
-      <c r="C32" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E32" s="4" t="s">
+      <c r="G31" s="13" t="s">
+        <v>412</v>
+      </c>
+      <c r="H31" s="13" t="s">
         <v>448</v>
       </c>
-      <c r="F32" s="1" t="s">
+    </row>
+    <row r="32" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A32" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="B32" s="13" t="s">
         <v>449</v>
       </c>
-      <c r="G32" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="H32" s="1" t="s">
+      <c r="C32" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E32" s="9" t="s">
         <v>450</v>
       </c>
+      <c r="F32" s="13" t="s">
+        <v>451</v>
+      </c>
+      <c r="G32" s="13" t="s">
+        <v>448</v>
+      </c>
+      <c r="H32" s="13" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>452</v>
-      </c>
-      <c r="F33" s="1" t="s">
+      <c r="A33" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="B33" s="13" t="s">
         <v>453</v>
       </c>
-      <c r="G33" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="H33" s="1" t="s">
+      <c r="C33" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E33" s="9" t="s">
         <v>454</v>
       </c>
-    </row>
-    <row r="34" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A34" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="B34" s="1" t="s">
+      <c r="F33" s="13" t="s">
         <v>455</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E34" s="4" t="s">
+      <c r="G33" s="13" t="s">
+        <v>412</v>
+      </c>
+      <c r="H33" s="13" t="s">
         <v>456</v>
       </c>
-      <c r="F34" s="1" t="s">
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="B34" s="13" t="s">
         <v>457</v>
       </c>
-      <c r="G34" s="1" t="s">
-        <v>454</v>
-      </c>
-      <c r="H34" s="1" t="s">
+      <c r="C34" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D34" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E34" s="9" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A35" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="B35" s="1" t="s">
+      <c r="F34" s="13" t="s">
         <v>459</v>
       </c>
-      <c r="C35" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E35" s="4" t="s">
+      <c r="G34" s="13" t="s">
+        <v>456</v>
+      </c>
+      <c r="H34" s="13" t="s">
         <v>460</v>
       </c>
-      <c r="F35" s="1" t="s">
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A35" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="B35" s="13" t="s">
         <v>461</v>
       </c>
-      <c r="G35" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="H35" s="1" t="s">
+      <c r="C35" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D35" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E35" s="9" t="s">
         <v>462</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A36" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="B36" s="1" t="s">
+      <c r="F35" s="13" t="s">
         <v>463</v>
       </c>
-      <c r="C36" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E36" s="4" t="s">
+      <c r="G35" s="13" t="s">
+        <v>412</v>
+      </c>
+      <c r="H35" s="13" t="s">
         <v>464</v>
       </c>
-      <c r="F36" s="1" t="s">
+    </row>
+    <row r="36" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A36" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="B36" s="13" t="s">
         <v>465</v>
       </c>
-      <c r="G36" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="H36" s="1" t="s">
+      <c r="C36" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D36" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E36" s="9" t="s">
         <v>466</v>
       </c>
+      <c r="F36" s="13" t="s">
+        <v>467</v>
+      </c>
+      <c r="G36" s="13" t="s">
+        <v>464</v>
+      </c>
+      <c r="H36" s="13" t="s">
+        <v>468</v>
+      </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>467</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E37" s="4" t="s">
-        <v>468</v>
-      </c>
-      <c r="F37" s="1" t="s">
+      <c r="A37" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="B37" s="13" t="s">
         <v>469</v>
       </c>
-      <c r="G37" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="H37" s="1" t="s">
+      <c r="C37" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D37" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E37" s="9" t="s">
         <v>470</v>
       </c>
+      <c r="F37" s="13" t="s">
+        <v>471</v>
+      </c>
+      <c r="G37" s="13" t="s">
+        <v>412</v>
+      </c>
+      <c r="H37" s="13" t="s">
+        <v>472</v>
+      </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A38" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>471</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E38" s="4" t="s">
+      <c r="A38" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="B38" s="13" t="s">
+        <v>473</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D38" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E38" s="9" t="s">
+        <v>474</v>
+      </c>
+      <c r="F38" s="13" t="s">
+        <v>475</v>
+      </c>
+      <c r="G38" s="13" t="s">
         <v>472</v>
       </c>
-      <c r="F38" s="1" t="s">
-        <v>473</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>470</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>474</v>
+      <c r="H38" s="13" t="s">
+        <v>476</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E39" s="4" t="s">
-        <v>476</v>
-      </c>
-      <c r="F39" s="1" t="s">
+      <c r="A39" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="B39" s="13" t="s">
         <v>477</v>
       </c>
-      <c r="G39" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="H39" s="1" t="s">
+      <c r="C39" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D39" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E39" s="9" t="s">
         <v>478</v>
       </c>
-    </row>
-    <row r="40" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A40" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="B40" s="1" t="s">
+      <c r="F39" s="13" t="s">
         <v>479</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E40" s="4" t="s">
+      <c r="G39" s="13" t="s">
+        <v>412</v>
+      </c>
+      <c r="H39" s="13" t="s">
         <v>480</v>
       </c>
-      <c r="F40" s="1" t="s">
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A40" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="B40" s="13" t="s">
         <v>481</v>
       </c>
-      <c r="G40" s="1" t="s">
-        <v>478</v>
-      </c>
-      <c r="H40" s="1" t="s">
+      <c r="C40" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D40" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E40" s="9" t="s">
         <v>482</v>
       </c>
+      <c r="F40" s="13" t="s">
+        <v>483</v>
+      </c>
+      <c r="G40" s="13" t="s">
+        <v>480</v>
+      </c>
+      <c r="H40" s="13" t="s">
+        <v>484</v>
+      </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>483</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E41" s="4" t="s">
-        <v>484</v>
-      </c>
-      <c r="F41" s="1" t="s">
+      <c r="A41" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="B41" s="13" t="s">
         <v>485</v>
       </c>
-      <c r="G41" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="H41" s="1" t="s">
+      <c r="C41" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D41" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E41" s="9" t="s">
         <v>486</v>
       </c>
+      <c r="F41" s="13" t="s">
+        <v>487</v>
+      </c>
+      <c r="G41" s="13" t="s">
+        <v>412</v>
+      </c>
+      <c r="H41" s="13" t="s">
+        <v>488</v>
+      </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E42" s="4" t="s">
+      <c r="A42" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="B42" s="13" t="s">
+        <v>489</v>
+      </c>
+      <c r="C42" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D42" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E42" s="9" t="s">
+        <v>490</v>
+      </c>
+      <c r="F42" s="13" t="s">
+        <v>491</v>
+      </c>
+      <c r="G42" s="13" t="s">
         <v>488</v>
       </c>
-      <c r="F42" s="1" t="s">
-        <v>489</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>486</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>490</v>
+      <c r="H42" s="13" t="s">
+        <v>492</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A43" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>491</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>492</v>
-      </c>
-      <c r="F43" s="1" t="s">
+      <c r="A43" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="B43" s="13" t="s">
         <v>493</v>
       </c>
-      <c r="G43" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="H43" s="1" t="s">
+      <c r="C43" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D43" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E43" s="9" t="s">
         <v>494</v>
       </c>
+      <c r="F43" s="13" t="s">
+        <v>495</v>
+      </c>
+      <c r="G43" s="13" t="s">
+        <v>412</v>
+      </c>
+      <c r="H43" s="13" t="s">
+        <v>496</v>
+      </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A44" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>495</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E44" s="4" t="s">
+      <c r="A44" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="B44" s="13" t="s">
+        <v>497</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D44" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E44" s="9" t="s">
+        <v>498</v>
+      </c>
+      <c r="F44" s="13" t="s">
+        <v>499</v>
+      </c>
+      <c r="G44" s="13" t="s">
         <v>496</v>
       </c>
-      <c r="F44" s="1" t="s">
-        <v>497</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>494</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>498</v>
+      <c r="H44" s="13" t="s">
+        <v>500</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A45" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E45" s="4" t="s">
-        <v>500</v>
-      </c>
-      <c r="F45" s="1" t="s">
+      <c r="A45" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="B45" s="13" t="s">
         <v>501</v>
       </c>
-      <c r="G45" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="H45" s="1" t="s">
+      <c r="C45" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D45" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E45" s="9" t="s">
         <v>502</v>
       </c>
+      <c r="F45" s="13" t="s">
+        <v>503</v>
+      </c>
+      <c r="G45" s="13" t="s">
+        <v>412</v>
+      </c>
+      <c r="H45" s="13" t="s">
+        <v>504</v>
+      </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A46" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>503</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E46" s="4" t="s">
+      <c r="A46" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="C46" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D46" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E46" s="9" t="s">
+        <v>506</v>
+      </c>
+      <c r="F46" s="13" t="s">
+        <v>507</v>
+      </c>
+      <c r="G46" s="13" t="s">
         <v>504</v>
       </c>
-      <c r="F46" s="1" t="s">
-        <v>505</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A47" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E47" s="4" t="s">
+      <c r="H46" s="13" t="s">
         <v>508</v>
       </c>
-      <c r="F47" s="1" t="s">
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A47" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="B47" s="13" t="s">
         <v>509</v>
       </c>
-      <c r="G47" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="H47" s="1" t="s">
+      <c r="C47" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D47" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E47" s="9" t="s">
         <v>510</v>
       </c>
-    </row>
-    <row r="48" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A48" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="B48" s="1" t="s">
+      <c r="F47" s="13" t="s">
         <v>511</v>
       </c>
-      <c r="C48" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E48" s="4" t="s">
+      <c r="G47" s="13" t="s">
+        <v>412</v>
+      </c>
+      <c r="H47" s="13" t="s">
         <v>512</v>
       </c>
-      <c r="F48" s="1" t="s">
+    </row>
+    <row r="48" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A48" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="B48" s="13" t="s">
         <v>513</v>
       </c>
-      <c r="G48" s="1" t="s">
-        <v>510</v>
-      </c>
-      <c r="H48" s="1" t="s">
+      <c r="C48" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D48" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E48" s="9" t="s">
         <v>514</v>
       </c>
+      <c r="F48" s="13" t="s">
+        <v>515</v>
+      </c>
+      <c r="G48" s="13" t="s">
+        <v>512</v>
+      </c>
+      <c r="H48" s="13" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A49" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>515</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E49" s="4" t="s">
-        <v>516</v>
-      </c>
-      <c r="F49" s="1" t="s">
+      <c r="A49" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="B49" s="13" t="s">
         <v>517</v>
       </c>
-      <c r="G49" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="H49" s="1" t="s">
+      <c r="C49" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D49" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E49" s="9" t="s">
         <v>518</v>
       </c>
+      <c r="F49" s="13" t="s">
+        <v>519</v>
+      </c>
+      <c r="G49" s="13" t="s">
+        <v>412</v>
+      </c>
+      <c r="H49" s="13" t="s">
+        <v>520</v>
+      </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A50" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E50" s="4" t="s">
+      <c r="A50" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>521</v>
+      </c>
+      <c r="C50" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D50" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E50" s="9" t="s">
+        <v>522</v>
+      </c>
+      <c r="F50" s="13" t="s">
+        <v>523</v>
+      </c>
+      <c r="G50" s="13" t="s">
         <v>520</v>
       </c>
-      <c r="F50" s="1" t="s">
-        <v>521</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>518</v>
-      </c>
-      <c r="H50" s="1" t="s">
-        <v>522</v>
+      <c r="H50" s="13" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A51" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>523</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E51" s="4" t="s">
-        <v>524</v>
-      </c>
-      <c r="F51" s="1" t="s">
+      <c r="A51" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B51" s="13" t="s">
         <v>525</v>
       </c>
-      <c r="G51" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="H51" s="1" t="s">
+      <c r="C51" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D51" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E51" s="9" t="s">
         <v>526</v>
       </c>
-    </row>
-    <row r="52" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A52" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="B52" s="1" t="s">
+      <c r="F51" s="13" t="s">
         <v>527</v>
       </c>
-      <c r="C52" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E52" s="4" t="s">
+      <c r="G51" s="13" t="s">
+        <v>412</v>
+      </c>
+      <c r="H51" s="13" t="s">
         <v>528</v>
       </c>
-      <c r="F52" s="1" t="s">
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A52" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="B52" s="13" t="s">
         <v>529</v>
       </c>
-      <c r="G52" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="H52" s="1" t="s">
+      <c r="C52" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D52" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E52" s="9" t="s">
         <v>530</v>
       </c>
-    </row>
-    <row r="53" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A53" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="B53" s="1" t="s">
+      <c r="F52" s="13" t="s">
         <v>531</v>
       </c>
-      <c r="C53" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E53" s="4" t="s">
+      <c r="G52" s="13" t="s">
+        <v>528</v>
+      </c>
+      <c r="H52" s="13" t="s">
         <v>532</v>
       </c>
-      <c r="F53" s="1" t="s">
+    </row>
+    <row r="53" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A53" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="B53" s="13" t="s">
         <v>533</v>
       </c>
-      <c r="G53" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="H53" s="1" t="s">
+      <c r="C53" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D53" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E53" s="9" t="s">
         <v>534</v>
       </c>
-    </row>
-    <row r="54" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A54" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="B54" s="1" t="s">
+      <c r="F53" s="13" t="s">
         <v>535</v>
       </c>
-      <c r="C54" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E54" s="4" t="s">
+      <c r="G53" s="13" t="s">
+        <v>412</v>
+      </c>
+      <c r="H53" s="13" t="s">
         <v>536</v>
       </c>
-      <c r="F54" s="1" t="s">
+    </row>
+    <row r="54" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A54" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="B54" s="13" t="s">
         <v>537</v>
       </c>
-      <c r="G54" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="H54" s="1" t="s">
+      <c r="C54" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D54" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E54" s="9" t="s">
         <v>538</v>
       </c>
-    </row>
-    <row r="55" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A55" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="B55" s="1" t="s">
+      <c r="F54" s="13" t="s">
         <v>539</v>
       </c>
-      <c r="C55" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E55" s="4" t="s">
+      <c r="G54" s="13" t="s">
+        <v>536</v>
+      </c>
+      <c r="H54" s="13" t="s">
         <v>540</v>
       </c>
-      <c r="F55" s="1" t="s">
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A55" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="B55" s="13" t="s">
         <v>541</v>
       </c>
-      <c r="G55" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="H55" s="1" t="s">
+      <c r="C55" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D55" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E55" s="9" t="s">
         <v>542</v>
       </c>
-    </row>
-    <row r="56" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A56" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="B56" s="1" t="s">
+      <c r="F55" s="13" t="s">
         <v>543</v>
       </c>
-      <c r="C56" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E56" s="4" t="s">
+      <c r="G55" s="13" t="s">
+        <v>412</v>
+      </c>
+      <c r="H55" s="13" t="s">
         <v>544</v>
       </c>
-      <c r="F56" s="1" t="s">
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A56" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="B56" s="13" t="s">
         <v>545</v>
       </c>
-      <c r="G56" s="1" t="s">
-        <v>542</v>
-      </c>
-      <c r="H56" s="1" t="s">
+      <c r="C56" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D56" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E56" s="9" t="s">
         <v>546</v>
       </c>
-    </row>
-    <row r="57" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A57" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="B57" s="1" t="s">
+      <c r="F56" s="13" t="s">
         <v>547</v>
       </c>
-      <c r="C57" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E57" s="4" t="s">
+      <c r="G56" s="13" t="s">
+        <v>544</v>
+      </c>
+      <c r="H56" s="13" t="s">
         <v>548</v>
       </c>
-      <c r="F57" s="1" t="s">
+    </row>
+    <row r="57" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A57" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="B57" s="13" t="s">
         <v>549</v>
       </c>
-      <c r="G57" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="H57" s="1" t="s">
+      <c r="C57" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D57" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E57" s="9" t="s">
         <v>550</v>
       </c>
-    </row>
-    <row r="58" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A58" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="B58" s="1" t="s">
+      <c r="F57" s="13" t="s">
         <v>551</v>
       </c>
-      <c r="C58" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E58" s="4" t="s">
+      <c r="G57" s="13" t="s">
+        <v>412</v>
+      </c>
+      <c r="H57" s="13" t="s">
         <v>552</v>
       </c>
-      <c r="F58" s="1" t="s">
+    </row>
+    <row r="58" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A58" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="B58" s="13" t="s">
         <v>553</v>
       </c>
-      <c r="G58" s="1" t="s">
-        <v>550</v>
-      </c>
-      <c r="H58" s="1" t="s">
+      <c r="C58" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D58" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E58" s="9" t="s">
         <v>554</v>
       </c>
+      <c r="F58" s="13" t="s">
+        <v>555</v>
+      </c>
+      <c r="G58" s="13" t="s">
+        <v>552</v>
+      </c>
+      <c r="H58" s="13" t="s">
+        <v>556</v>
+      </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A59" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>555</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E59" s="4" t="s">
-        <v>556</v>
-      </c>
-      <c r="F59" s="1" t="s">
+      <c r="A59" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="B59" s="13" t="s">
         <v>557</v>
       </c>
-      <c r="G59" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="H59" s="1" t="s">
+      <c r="C59" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D59" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E59" s="9" t="s">
         <v>558</v>
       </c>
+      <c r="F59" s="13" t="s">
+        <v>559</v>
+      </c>
+      <c r="G59" s="13" t="s">
+        <v>412</v>
+      </c>
+      <c r="H59" s="13" t="s">
+        <v>560</v>
+      </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A60" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>559</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E60" s="4" t="s">
+      <c r="A60" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="B60" s="13" t="s">
+        <v>561</v>
+      </c>
+      <c r="C60" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D60" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E60" s="9" t="s">
+        <v>562</v>
+      </c>
+      <c r="F60" s="13" t="s">
+        <v>563</v>
+      </c>
+      <c r="G60" s="13" t="s">
         <v>560</v>
       </c>
-      <c r="F60" s="1" t="s">
-        <v>561</v>
-      </c>
-      <c r="G60" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="H60" s="1" t="s">
-        <v>562</v>
+      <c r="H60" s="13" t="s">
+        <v>564</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A61" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>563</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E61" s="4" t="s">
-        <v>564</v>
-      </c>
-      <c r="F61" s="1" t="s">
+      <c r="A61" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="B61" s="13" t="s">
         <v>565</v>
       </c>
-      <c r="G61" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="H61" s="1" t="s">
+      <c r="C61" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D61" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E61" s="9" t="s">
         <v>566</v>
       </c>
+      <c r="F61" s="13" t="s">
+        <v>567</v>
+      </c>
+      <c r="G61" s="13" t="s">
+        <v>412</v>
+      </c>
+      <c r="H61" s="13" t="s">
+        <v>568</v>
+      </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A62" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E62" s="4" t="s">
+      <c r="A62" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="B62" s="13" t="s">
+        <v>569</v>
+      </c>
+      <c r="C62" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D62" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E62" s="9" t="s">
+        <v>570</v>
+      </c>
+      <c r="F62" s="13" t="s">
+        <v>571</v>
+      </c>
+      <c r="G62" s="13" t="s">
         <v>568</v>
       </c>
-      <c r="F62" s="1" t="s">
-        <v>569</v>
-      </c>
-      <c r="G62" s="1" t="s">
-        <v>566</v>
-      </c>
-      <c r="H62" s="1" t="s">
-        <v>570</v>
+      <c r="H62" s="13" t="s">
+        <v>572</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A63" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>571</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E63" s="4" t="s">
-        <v>572</v>
-      </c>
-      <c r="F63" s="1" t="s">
+      <c r="A63" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="B63" s="13" t="s">
         <v>573</v>
       </c>
-      <c r="G63" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="H63" s="1" t="s">
+      <c r="C63" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D63" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E63" s="9" t="s">
         <v>574</v>
       </c>
-    </row>
-    <row r="64" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A64" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="B64" s="1" t="s">
+      <c r="F63" s="13" t="s">
         <v>575</v>
       </c>
-      <c r="C64" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E64" s="4" t="s">
+      <c r="G63" s="13" t="s">
+        <v>412</v>
+      </c>
+      <c r="H63" s="13" t="s">
         <v>576</v>
       </c>
-      <c r="F64" s="1" t="s">
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A64" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="B64" s="13" t="s">
         <v>577</v>
       </c>
-      <c r="G64" s="1" t="s">
-        <v>574</v>
-      </c>
-      <c r="H64" s="1" t="s">
+      <c r="C64" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D64" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E64" s="9" t="s">
         <v>578</v>
       </c>
+      <c r="F64" s="13" t="s">
+        <v>579</v>
+      </c>
+      <c r="G64" s="13" t="s">
+        <v>576</v>
+      </c>
+      <c r="H64" s="13" t="s">
+        <v>580</v>
+      </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A65" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>579</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E65" s="4" t="s">
-        <v>580</v>
-      </c>
-      <c r="F65" s="1" t="s">
+      <c r="A65" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="B65" s="13" t="s">
         <v>581</v>
       </c>
-      <c r="G65" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="H65" s="1" t="s">
+      <c r="C65" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D65" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E65" s="9" t="s">
         <v>582</v>
       </c>
+      <c r="F65" s="13" t="s">
+        <v>583</v>
+      </c>
+      <c r="G65" s="13" t="s">
+        <v>412</v>
+      </c>
+      <c r="H65" s="13" t="s">
+        <v>584</v>
+      </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A66" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>583</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E66" s="4" t="s">
+      <c r="A66" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="B66" s="13" t="s">
+        <v>585</v>
+      </c>
+      <c r="C66" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D66" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E66" s="9" t="s">
+        <v>586</v>
+      </c>
+      <c r="F66" s="13" t="s">
+        <v>587</v>
+      </c>
+      <c r="G66" s="13" t="s">
         <v>584</v>
       </c>
-      <c r="F66" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="G66" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="H66" s="1" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A67" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>587</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E67" s="4" t="s">
+      <c r="H66" s="13" t="s">
         <v>588</v>
       </c>
-      <c r="F67" s="1" t="s">
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A67" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="B67" s="13" t="s">
         <v>589</v>
       </c>
-      <c r="G67" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="H67" s="1" t="s">
+      <c r="C67" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D67" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E67" s="9" t="s">
         <v>590</v>
       </c>
-    </row>
-    <row r="68" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A68" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="B68" s="1" t="s">
+      <c r="F67" s="13" t="s">
         <v>591</v>
       </c>
-      <c r="C68" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E68" s="4" t="s">
+      <c r="G67" s="13" t="s">
+        <v>412</v>
+      </c>
+      <c r="H67" s="13" t="s">
         <v>592</v>
       </c>
-      <c r="F68" s="1" t="s">
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A68" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="B68" s="13" t="s">
         <v>593</v>
       </c>
-      <c r="G68" s="1" t="s">
-        <v>590</v>
-      </c>
-      <c r="H68" s="1" t="s">
+      <c r="C68" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D68" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E68" s="9" t="s">
         <v>594</v>
       </c>
-    </row>
-    <row r="69" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A69" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="B69" s="1" t="s">
+      <c r="F68" s="13" t="s">
         <v>595</v>
       </c>
-      <c r="C69" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E69" s="4" t="s">
+      <c r="G68" s="13" t="s">
+        <v>592</v>
+      </c>
+      <c r="H68" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="F69" s="1" t="s">
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A69" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="B69" s="13" t="s">
         <v>597</v>
       </c>
-      <c r="G69" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="H69" s="1" t="s">
+      <c r="C69" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D69" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E69" s="9" t="s">
         <v>598</v>
       </c>
-    </row>
-    <row r="70" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A70" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="B70" s="1" t="s">
+      <c r="F69" s="13" t="s">
         <v>599</v>
       </c>
-      <c r="C70" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E70" s="4" t="s">
+      <c r="G69" s="13" t="s">
+        <v>412</v>
+      </c>
+      <c r="H69" s="13" t="s">
         <v>600</v>
       </c>
-      <c r="F70" s="1" t="s">
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A70" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="B70" s="13" t="s">
         <v>601</v>
       </c>
-      <c r="G70" s="1" t="s">
-        <v>598</v>
-      </c>
-      <c r="H70" s="1" t="s">
+      <c r="C70" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D70" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E70" s="9" t="s">
         <v>602</v>
       </c>
+      <c r="F70" s="13" t="s">
+        <v>603</v>
+      </c>
+      <c r="G70" s="13" t="s">
+        <v>600</v>
+      </c>
+      <c r="H70" s="13" t="s">
+        <v>604</v>
+      </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A71" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>603</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E71" s="4" t="s">
-        <v>604</v>
-      </c>
-      <c r="F71" s="1" t="s">
+      <c r="A71" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="B71" s="13" t="s">
         <v>605</v>
       </c>
-      <c r="G71" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="H71" s="1" t="s">
+      <c r="C71" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D71" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E71" s="9" t="s">
         <v>606</v>
       </c>
+      <c r="F71" s="13" t="s">
+        <v>607</v>
+      </c>
+      <c r="G71" s="13" t="s">
+        <v>412</v>
+      </c>
+      <c r="H71" s="13" t="s">
+        <v>608</v>
+      </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A72" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>607</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E72" s="4" t="s">
+      <c r="A72" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="B72" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="C72" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D72" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E72" s="9" t="s">
+        <v>610</v>
+      </c>
+      <c r="F72" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="G72" s="13" t="s">
         <v>608</v>
       </c>
-      <c r="F72" s="1" t="s">
-        <v>609</v>
-      </c>
-      <c r="G72" s="1" t="s">
-        <v>606</v>
-      </c>
-      <c r="H72" s="1" t="s">
-        <v>610</v>
+      <c r="H72" s="13" t="s">
+        <v>612</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A73" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>611</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E73" s="4" t="s">
-        <v>612</v>
-      </c>
-      <c r="F73" s="1" t="s">
+      <c r="A73" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="B73" s="13" t="s">
         <v>613</v>
       </c>
-      <c r="G73" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="H73" s="1" t="s">
+      <c r="C73" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D73" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E73" s="9" t="s">
         <v>614</v>
       </c>
+      <c r="F73" s="13" t="s">
+        <v>615</v>
+      </c>
+      <c r="G73" s="13" t="s">
+        <v>412</v>
+      </c>
+      <c r="H73" s="13" t="s">
+        <v>616</v>
+      </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A74" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>615</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E74" s="4" t="s">
+      <c r="A74" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="B74" s="13" t="s">
+        <v>617</v>
+      </c>
+      <c r="C74" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D74" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E74" s="9" t="s">
+        <v>618</v>
+      </c>
+      <c r="F74" s="13" t="s">
+        <v>619</v>
+      </c>
+      <c r="G74" s="13" t="s">
         <v>616</v>
       </c>
-      <c r="F74" s="1" t="s">
-        <v>617</v>
-      </c>
-      <c r="G74" s="1" t="s">
-        <v>614</v>
-      </c>
-      <c r="H74" s="1" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A75" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>619</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E75" s="4" t="s">
+      <c r="H74" s="13" t="s">
         <v>620</v>
       </c>
-      <c r="F75" s="1" t="s">
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A75" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="B75" s="13" t="s">
         <v>621</v>
       </c>
-      <c r="G75" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="H75" s="1" t="s">
+      <c r="C75" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D75" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E75" s="9" t="s">
         <v>622</v>
       </c>
-    </row>
-    <row r="76" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A76" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="B76" s="1" t="s">
+      <c r="F75" s="13" t="s">
         <v>623</v>
       </c>
-      <c r="C76" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E76" s="4" t="s">
+      <c r="G75" s="13" t="s">
+        <v>412</v>
+      </c>
+      <c r="H75" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="F76" s="1" t="s">
+    </row>
+    <row r="76" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A76" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="B76" s="13" t="s">
         <v>625</v>
       </c>
-      <c r="G76" s="1" t="s">
-        <v>622</v>
-      </c>
-      <c r="H76" s="1" t="s">
+      <c r="C76" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D76" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E76" s="9" t="s">
         <v>626</v>
       </c>
+      <c r="F76" s="13" t="s">
+        <v>627</v>
+      </c>
+      <c r="G76" s="13" t="s">
+        <v>624</v>
+      </c>
+      <c r="H76" s="13" t="s">
+        <v>628</v>
+      </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A77" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>627</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E77" s="4" t="s">
-        <v>628</v>
-      </c>
-      <c r="F77" s="1" t="s">
+      <c r="A77" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="B77" s="13" t="s">
         <v>629</v>
       </c>
-      <c r="G77" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="H77" s="1" t="s">
+      <c r="C77" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D77" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E77" s="9" t="s">
         <v>630</v>
       </c>
+      <c r="F77" s="13" t="s">
+        <v>631</v>
+      </c>
+      <c r="G77" s="13" t="s">
+        <v>412</v>
+      </c>
+      <c r="H77" s="13" t="s">
+        <v>632</v>
+      </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A78" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>631</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E78" s="4" t="s">
+      <c r="A78" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="B78" s="13" t="s">
+        <v>633</v>
+      </c>
+      <c r="C78" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D78" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E78" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="F78" s="13" t="s">
+        <v>635</v>
+      </c>
+      <c r="G78" s="13" t="s">
         <v>632</v>
       </c>
-      <c r="F78" s="1" t="s">
-        <v>633</v>
-      </c>
-      <c r="G78" s="1" t="s">
-        <v>630</v>
-      </c>
-      <c r="H78" s="1" t="s">
-        <v>634</v>
+      <c r="H78" s="13" t="s">
+        <v>636</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A79" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>635</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E79" s="4" t="s">
-        <v>636</v>
-      </c>
-      <c r="F79" s="1" t="s">
+      <c r="A79" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="B79" s="13" t="s">
         <v>637</v>
       </c>
-      <c r="G79" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="H79" s="1" t="s">
+      <c r="C79" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D79" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E79" s="9" t="s">
         <v>638</v>
       </c>
+      <c r="F79" s="13" t="s">
+        <v>639</v>
+      </c>
+      <c r="G79" s="13" t="s">
+        <v>412</v>
+      </c>
+      <c r="H79" s="13" t="s">
+        <v>640</v>
+      </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A80" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>639</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E80" s="4" t="s">
+      <c r="A80" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="B80" s="13" t="s">
+        <v>641</v>
+      </c>
+      <c r="C80" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D80" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E80" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="F80" s="13" t="s">
+        <v>643</v>
+      </c>
+      <c r="G80" s="13" t="s">
         <v>640</v>
       </c>
-      <c r="F80" s="1" t="s">
-        <v>641</v>
-      </c>
-      <c r="G80" s="1" t="s">
-        <v>638</v>
-      </c>
-      <c r="H80" s="1" t="s">
-        <v>642</v>
+      <c r="H80" s="13" t="s">
+        <v>644</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A81" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>643</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E81" s="4" t="s">
-        <v>644</v>
-      </c>
-      <c r="F81" s="1" t="s">
+      <c r="A81" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="B81" s="13" t="s">
         <v>645</v>
       </c>
-      <c r="G81" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="H81" s="1" t="s">
+      <c r="C81" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D81" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E81" s="9" t="s">
         <v>646</v>
       </c>
+      <c r="F81" s="13" t="s">
+        <v>647</v>
+      </c>
+      <c r="G81" s="13" t="s">
+        <v>412</v>
+      </c>
+      <c r="H81" s="13" t="s">
+        <v>648</v>
+      </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A82" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>647</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E82" s="4" t="s">
+      <c r="A82" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="B82" s="13" t="s">
+        <v>649</v>
+      </c>
+      <c r="C82" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D82" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E82" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="F82" s="13" t="s">
+        <v>651</v>
+      </c>
+      <c r="G82" s="13" t="s">
         <v>648</v>
       </c>
-      <c r="F82" s="1" t="s">
-        <v>649</v>
-      </c>
-      <c r="G82" s="1" t="s">
-        <v>646</v>
-      </c>
-      <c r="H82" s="1" t="s">
-        <v>650</v>
+      <c r="H82" s="13" t="s">
+        <v>652</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A83" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>651</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E83" s="4" t="s">
-        <v>652</v>
-      </c>
-      <c r="F83" s="1" t="s">
+      <c r="A83" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="B83" s="13" t="s">
         <v>653</v>
       </c>
-      <c r="G83" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="H83" s="1" t="s">
+      <c r="C83" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D83" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E83" s="9" t="s">
         <v>654</v>
       </c>
+      <c r="F83" s="13" t="s">
+        <v>655</v>
+      </c>
+      <c r="G83" s="13" t="s">
+        <v>412</v>
+      </c>
+      <c r="H83" s="13" t="s">
+        <v>656</v>
+      </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A84" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>655</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E84" s="4" t="s">
+      <c r="A84" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="B84" s="13" t="s">
+        <v>657</v>
+      </c>
+      <c r="C84" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D84" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E84" s="9" t="s">
+        <v>658</v>
+      </c>
+      <c r="F84" s="13" t="s">
+        <v>659</v>
+      </c>
+      <c r="G84" s="13" t="s">
         <v>656</v>
       </c>
-      <c r="F84" s="1" t="s">
-        <v>657</v>
-      </c>
-      <c r="G84" s="1" t="s">
-        <v>654</v>
-      </c>
-      <c r="H84" s="1" t="s">
-        <v>658</v>
+      <c r="H84" s="13" t="s">
+        <v>660</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A85" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>659</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E85" s="4" t="s">
-        <v>660</v>
-      </c>
-      <c r="F85" s="1" t="s">
+      <c r="A85" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="B85" s="13" t="s">
         <v>661</v>
       </c>
-      <c r="G85" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="H85" s="1" t="s">
+      <c r="C85" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D85" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E85" s="9" t="s">
         <v>662</v>
       </c>
-    </row>
-    <row r="86" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A86" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="B86" s="1" t="s">
+      <c r="F85" s="13" t="s">
         <v>663</v>
       </c>
-      <c r="C86" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E86" s="4" t="s">
+      <c r="G85" s="13" t="s">
+        <v>412</v>
+      </c>
+      <c r="H85" s="13" t="s">
         <v>664</v>
       </c>
-      <c r="F86" s="1" t="s">
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A86" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="B86" s="13" t="s">
         <v>665</v>
       </c>
-      <c r="G86" s="1" t="s">
-        <v>662</v>
-      </c>
-      <c r="H86" s="1" t="s">
+      <c r="C86" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D86" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E86" s="9" t="s">
         <v>666</v>
       </c>
-    </row>
-    <row r="87" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A87" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="B87" s="1" t="s">
+      <c r="F86" s="13" t="s">
         <v>667</v>
       </c>
-      <c r="C87" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E87" s="4" t="s">
+      <c r="G86" s="13" t="s">
+        <v>664</v>
+      </c>
+      <c r="H86" s="13" t="s">
         <v>668</v>
       </c>
-      <c r="F87" s="1" t="s">
+    </row>
+    <row r="87" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A87" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="B87" s="13" t="s">
         <v>669</v>
       </c>
-      <c r="G87" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="H87" s="1" t="s">
+      <c r="C87" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D87" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E87" s="9" t="s">
         <v>670</v>
       </c>
-    </row>
-    <row r="88" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A88" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="B88" s="1" t="s">
+      <c r="F87" s="13" t="s">
         <v>671</v>
       </c>
-      <c r="C88" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E88" s="4" t="s">
+      <c r="G87" s="13" t="s">
+        <v>412</v>
+      </c>
+      <c r="H87" s="13" t="s">
         <v>672</v>
       </c>
-      <c r="F88" s="1" t="s">
+    </row>
+    <row r="88" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A88" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="B88" s="13" t="s">
         <v>673</v>
       </c>
-      <c r="G88" s="1" t="s">
-        <v>670</v>
-      </c>
-      <c r="H88" s="1" t="s">
+      <c r="C88" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D88" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E88" s="9" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="89" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A89" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="B89" s="1" t="s">
+      <c r="F88" s="13" t="s">
         <v>675</v>
       </c>
-      <c r="C89" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E89" s="4" t="s">
+      <c r="G88" s="13" t="s">
+        <v>672</v>
+      </c>
+      <c r="H88" s="13" t="s">
         <v>676</v>
       </c>
-      <c r="F89" s="1" t="s">
+    </row>
+    <row r="89" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A89" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="B89" s="13" t="s">
         <v>677</v>
       </c>
-      <c r="G89" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="H89" s="1" t="s">
+      <c r="C89" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D89" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E89" s="9" t="s">
         <v>678</v>
       </c>
-    </row>
-    <row r="90" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A90" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="B90" s="1" t="s">
+      <c r="F89" s="13" t="s">
         <v>679</v>
       </c>
-      <c r="C90" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E90" s="4" t="s">
+      <c r="G89" s="13" t="s">
+        <v>412</v>
+      </c>
+      <c r="H89" s="13" t="s">
         <v>680</v>
       </c>
-      <c r="F90" s="1" t="s">
+    </row>
+    <row r="90" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A90" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="B90" s="13" t="s">
         <v>681</v>
       </c>
-      <c r="G90" s="1" t="s">
-        <v>678</v>
-      </c>
-      <c r="H90" s="1" t="s">
+      <c r="C90" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D90" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E90" s="9" t="s">
         <v>682</v>
       </c>
-    </row>
-    <row r="91" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A91" s="4" t="s">
+      <c r="F90" s="13" t="s">
         <v>683</v>
       </c>
-      <c r="B91" s="1" t="s">
+      <c r="G90" s="13" t="s">
+        <v>680</v>
+      </c>
+      <c r="H90" s="13" t="s">
         <v>684</v>
       </c>
-      <c r="C91" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E91" s="4" t="s">
+    </row>
+    <row r="91" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A91" s="9" t="s">
         <v>685</v>
       </c>
-      <c r="F91" s="1" t="s">
+      <c r="B91" s="13" t="s">
         <v>686</v>
       </c>
-      <c r="G91" s="1" t="s">
-        <v>682</v>
-      </c>
-      <c r="H91" s="1" t="s">
+      <c r="C91" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D91" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E91" s="9" t="s">
         <v>687</v>
       </c>
+      <c r="F91" s="13" t="s">
+        <v>688</v>
+      </c>
+      <c r="G91" s="13" t="s">
+        <v>684</v>
+      </c>
+      <c r="H91" s="13" t="s">
+        <v>689</v>
+      </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A92" s="4" t="s">
-        <v>688</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>689</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E92" s="4" t="s">
+      <c r="A92" s="9" t="s">
         <v>690</v>
       </c>
-      <c r="F92" s="1" t="s">
+      <c r="B92" s="13" t="s">
         <v>691</v>
       </c>
-      <c r="G92" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="H92" s="1" t="s">
+      <c r="C92" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D92" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E92" s="9" t="s">
         <v>692</v>
       </c>
+      <c r="F92" s="13" t="s">
+        <v>693</v>
+      </c>
+      <c r="G92" s="13" t="s">
+        <v>412</v>
+      </c>
+      <c r="H92" s="13" t="s">
+        <v>694</v>
+      </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A93" s="4" t="s">
-        <v>693</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>694</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E93" s="4" t="s">
+      <c r="A93" s="9" t="s">
         <v>695</v>
       </c>
-      <c r="F93" s="1" t="s">
+      <c r="B93" s="13" t="s">
         <v>696</v>
       </c>
-      <c r="G93" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="H93" s="1" t="s">
+      <c r="C93" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D93" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E93" s="9" t="s">
         <v>697</v>
       </c>
-    </row>
-    <row r="94" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A94" s="4" t="s">
+      <c r="F93" s="13" t="s">
         <v>698</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="G93" s="13" t="s">
+        <v>412</v>
+      </c>
+      <c r="H93" s="13" t="s">
         <v>699</v>
       </c>
-      <c r="C94" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E94" s="4" t="s">
+    </row>
+    <row r="94" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A94" s="9" t="s">
         <v>700</v>
       </c>
-      <c r="F94" s="1" t="s">
+      <c r="B94" s="13" t="s">
         <v>701</v>
       </c>
-      <c r="G94" s="1" t="s">
+      <c r="C94" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D94" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E94" s="9" t="s">
         <v>702</v>
       </c>
-      <c r="H94" s="1" t="s">
+      <c r="F94" s="13" t="s">
         <v>703</v>
       </c>
-    </row>
-    <row r="95" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A95" s="4" t="s">
+      <c r="G94" s="13" t="s">
         <v>704</v>
       </c>
-      <c r="B95" s="1" t="s">
+      <c r="H94" s="13" t="s">
         <v>705</v>
       </c>
-      <c r="C95" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E95" s="4" t="s">
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A95" s="9" t="s">
         <v>706</v>
       </c>
-      <c r="F95" s="1" t="s">
+      <c r="B95" s="13" t="s">
         <v>707</v>
       </c>
-      <c r="G95" s="1" t="s">
+      <c r="C95" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D95" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E95" s="9" t="s">
         <v>708</v>
       </c>
-      <c r="H95" s="1" t="s">
+      <c r="F95" s="13" t="s">
         <v>709</v>
       </c>
-    </row>
-    <row r="96" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A96" s="4" t="s">
+      <c r="G95" s="13" t="s">
         <v>710</v>
       </c>
-      <c r="B96" s="1" t="s">
+      <c r="H95" s="13" t="s">
         <v>711</v>
       </c>
-      <c r="C96" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E96" s="4" t="s">
+    </row>
+    <row r="96" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A96" s="9" t="s">
         <v>712</v>
       </c>
-      <c r="F96" s="1" t="s">
+      <c r="B96" s="13" t="s">
         <v>713</v>
       </c>
-      <c r="G96" s="1" t="s">
+      <c r="C96" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D96" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E96" s="9" t="s">
         <v>714</v>
       </c>
-      <c r="H96" s="1" t="s">
+      <c r="F96" s="13" t="s">
         <v>715</v>
       </c>
-    </row>
-    <row r="97" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A97" s="4" t="s">
+      <c r="G96" s="13" t="s">
         <v>716</v>
       </c>
-      <c r="B97" s="1" t="s">
+      <c r="H96" s="13" t="s">
         <v>717</v>
       </c>
-      <c r="C97" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E97" s="4" t="s">
+    </row>
+    <row r="97" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A97" s="9" t="s">
         <v>718</v>
       </c>
-      <c r="F97" s="1" t="s">
+      <c r="B97" s="13" t="s">
         <v>719</v>
       </c>
-      <c r="G97" s="1" t="s">
+      <c r="C97" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D97" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E97" s="9" t="s">
         <v>720</v>
       </c>
-      <c r="H97" s="1" t="s">
+      <c r="F97" s="13" t="s">
         <v>721</v>
       </c>
-    </row>
-    <row r="98" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A98" s="4" t="s">
+      <c r="G97" s="13" t="s">
         <v>722</v>
       </c>
-      <c r="B98" s="1" t="s">
+      <c r="H97" s="13" t="s">
         <v>723</v>
       </c>
-      <c r="C98" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E98" s="4" t="s">
+    </row>
+    <row r="98" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A98" s="9" t="s">
         <v>724</v>
       </c>
-      <c r="F98" s="1" t="s">
+      <c r="B98" s="13" t="s">
         <v>725</v>
       </c>
-      <c r="G98" s="1" t="s">
+      <c r="C98" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D98" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E98" s="9" t="s">
         <v>726</v>
       </c>
-      <c r="H98" s="1" t="s">
+      <c r="F98" s="13" t="s">
         <v>727</v>
       </c>
-    </row>
-    <row r="99" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A99" s="4" t="s">
+      <c r="G98" s="13" t="s">
         <v>728</v>
       </c>
-      <c r="B99" s="1" t="s">
+      <c r="H98" s="13" t="s">
         <v>729</v>
       </c>
-      <c r="C99" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E99" s="4" t="s">
+    </row>
+    <row r="99" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A99" s="9" t="s">
         <v>730</v>
       </c>
-      <c r="F99" s="1" t="s">
+      <c r="B99" s="13" t="s">
         <v>731</v>
       </c>
-      <c r="G99" s="1" t="s">
+      <c r="C99" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D99" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E99" s="9" t="s">
         <v>732</v>
       </c>
-      <c r="H99" s="1" t="s">
+      <c r="F99" s="13" t="s">
         <v>733</v>
       </c>
+      <c r="G99" s="13" t="s">
+        <v>734</v>
+      </c>
+      <c r="H99" s="13" t="s">
+        <v>735</v>
+      </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A100" s="4" t="s">
-        <v>734</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>735</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E100" s="4" t="s">
+      <c r="A100" s="9" t="s">
         <v>736</v>
       </c>
-      <c r="F100" s="1" t="s">
+      <c r="B100" s="13" t="s">
         <v>737</v>
       </c>
-      <c r="G100" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="H100" s="1" t="s">
+      <c r="C100" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D100" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E100" s="9" t="s">
         <v>738</v>
       </c>
-    </row>
-    <row r="101" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A101" s="4" t="s">
+      <c r="F100" s="13" t="s">
         <v>739</v>
       </c>
-      <c r="B101" s="1" t="s">
+      <c r="G100" s="13" t="s">
+        <v>412</v>
+      </c>
+      <c r="H100" s="13" t="s">
         <v>740</v>
       </c>
-      <c r="C101" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E101" s="4" t="s">
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A101" s="9" t="s">
         <v>741</v>
       </c>
-      <c r="F101" s="1" t="s">
+      <c r="B101" s="13" t="s">
         <v>742</v>
       </c>
-      <c r="G101" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="H101" s="1" t="s">
+      <c r="C101" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D101" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E101" s="9" t="s">
         <v>743</v>
       </c>
-    </row>
-    <row r="102" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A102" s="4" t="s">
+      <c r="F101" s="13" t="s">
         <v>744</v>
       </c>
-      <c r="B102" s="1" t="s">
+      <c r="G101" s="13" t="s">
+        <v>412</v>
+      </c>
+      <c r="H101" s="13" t="s">
         <v>745</v>
       </c>
-      <c r="C102" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E102" s="4" t="s">
+    </row>
+    <row r="102" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A102" s="9" t="s">
         <v>746</v>
       </c>
-      <c r="F102" s="1" t="s">
+      <c r="B102" s="13" t="s">
         <v>747</v>
       </c>
-      <c r="G102" s="1" t="s">
+      <c r="C102" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D102" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E102" s="9" t="s">
         <v>748</v>
       </c>
-      <c r="H102" s="1" t="s">
+      <c r="F102" s="13" t="s">
         <v>749</v>
       </c>
-    </row>
-    <row r="103" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A103" s="4" t="s">
+      <c r="G102" s="13" t="s">
         <v>750</v>
       </c>
-      <c r="B103" s="1" t="s">
+      <c r="H102" s="13" t="s">
         <v>751</v>
       </c>
-      <c r="C103" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E103" s="4" t="s">
+    </row>
+    <row r="103" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A103" s="9" t="s">
         <v>752</v>
       </c>
-      <c r="F103" s="1" t="s">
+      <c r="B103" s="13" t="s">
         <v>753</v>
       </c>
-      <c r="G103" s="1" t="s">
+      <c r="C103" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D103" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E103" s="9" t="s">
         <v>754</v>
       </c>
-      <c r="H103" s="1" t="s">
+      <c r="F103" s="13" t="s">
         <v>755</v>
       </c>
-    </row>
-    <row r="104" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A104" s="4" t="s">
+      <c r="G103" s="13" t="s">
         <v>756</v>
       </c>
-      <c r="B104" s="1" t="s">
+      <c r="H103" s="13" t="s">
         <v>757</v>
       </c>
-      <c r="C104" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E104" s="4" t="s">
+    </row>
+    <row r="104" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A104" s="9" t="s">
         <v>758</v>
       </c>
-      <c r="F104" s="1" t="s">
+      <c r="B104" s="13" t="s">
         <v>759</v>
       </c>
-      <c r="G104" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="H104" s="1" t="s">
+      <c r="C104" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D104" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E104" s="9" t="s">
         <v>760</v>
       </c>
-    </row>
-    <row r="105" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A105" s="4" t="s">
+      <c r="F104" s="13" t="s">
         <v>761</v>
       </c>
-      <c r="B105" s="1" t="s">
+      <c r="G104" s="13" t="s">
+        <v>412</v>
+      </c>
+      <c r="H104" s="13" t="s">
         <v>762</v>
       </c>
-      <c r="C105" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E105" s="4" t="s">
+    </row>
+    <row r="105" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A105" s="9" t="s">
         <v>763</v>
       </c>
-      <c r="F105" s="1" t="s">
+      <c r="B105" s="13" t="s">
         <v>764</v>
       </c>
-      <c r="G105" s="1" t="s">
+      <c r="C105" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D105" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E105" s="9" t="s">
         <v>765</v>
       </c>
-      <c r="H105" s="1" t="s">
+      <c r="F105" s="13" t="s">
         <v>766</v>
       </c>
-    </row>
-    <row r="106" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A106" s="4" t="s">
+      <c r="G105" s="13" t="s">
         <v>767</v>
       </c>
-      <c r="B106" s="1" t="s">
+      <c r="H105" s="13" t="s">
         <v>768</v>
       </c>
-      <c r="C106" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E106" s="4" t="s">
+    </row>
+    <row r="106" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A106" s="8" t="s">
         <v>769</v>
       </c>
-      <c r="F106" s="1" t="s">
+      <c r="B106" s="12" t="s">
         <v>770</v>
       </c>
-      <c r="G106" s="1" t="s">
+      <c r="C106" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="D106" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="E106" s="8" t="s">
         <v>771</v>
       </c>
-      <c r="H106" s="1" t="s">
+      <c r="F106" s="12" t="s">
         <v>772</v>
+      </c>
+      <c r="G106" s="12" t="s">
+        <v>773</v>
+      </c>
+      <c r="H106" s="12" t="s">
+        <v>774</v>
       </c>
     </row>
   </sheetData>
@@ -7226,154 +7342,145 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3100EBA1-3EC6-4078-A42A-45F78C5B455D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90B342CD-2BB4-49BF-8789-5ECAA2AF0E72}">
   <dimension ref="A1:B21"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.77734375" customWidth="1"/>
-    <col min="2" max="2" width="76.77734375" customWidth="1"/>
+    <col min="1" max="1" width="26.77734375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="80.77734375" style="1" customWidth="1"/>
+    <col min="3" max="16384" width="11.5546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
-        <v>773</v>
-      </c>
-      <c r="B1" s="7"/>
+    <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="16" t="s">
+        <v>775</v>
+      </c>
+      <c r="B1" s="16"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>774</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>775</v>
+      <c r="A2" s="20"/>
+      <c r="B2" s="21" t="s">
+        <v>776</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>776</v>
-      </c>
-      <c r="B3" s="1" t="s">
+      <c r="A3" s="13" t="s">
         <v>777</v>
       </c>
+      <c r="B3" s="13" t="s">
+        <v>778</v>
+      </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>778</v>
-      </c>
-      <c r="B4" s="1" t="s">
+      <c r="A4" s="13" t="s">
         <v>779</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+      <c r="B4" s="13" t="s">
         <v>780</v>
       </c>
-      <c r="B5" s="1" t="s">
+    </row>
+    <row r="5" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="13" t="s">
         <v>781</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+      <c r="B5" s="13" t="s">
         <v>782</v>
       </c>
-      <c r="B6" s="1" t="s">
+    </row>
+    <row r="6" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="13" t="s">
         <v>783</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+      <c r="B6" s="13" t="s">
         <v>784</v>
       </c>
-      <c r="B7" s="1" t="s">
+    </row>
+    <row r="7" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="12" t="s">
         <v>785</v>
       </c>
+      <c r="B7" s="12" t="s">
+        <v>786</v>
+      </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>786</v>
-      </c>
-      <c r="B9" s="1" t="s">
+      <c r="A9" s="20"/>
+      <c r="B9" s="21" t="s">
         <v>787</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>776</v>
-      </c>
-      <c r="B10" s="1" t="s">
+      <c r="A10" s="13" t="s">
+        <v>777</v>
+      </c>
+      <c r="B10" s="13" t="s">
         <v>788</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="13" t="s">
         <v>789</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="13" t="s">
         <v>790</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>780</v>
-      </c>
-      <c r="B12" s="1" t="s">
+    <row r="12" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="13" t="s">
+        <v>781</v>
+      </c>
+      <c r="B12" s="13" t="s">
         <v>791</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
-        <v>784</v>
-      </c>
-      <c r="B13" s="1" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="12" t="s">
+        <v>785</v>
+      </c>
+      <c r="B13" s="12" t="s">
         <v>792</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="20"/>
+      <c r="B15" s="21" t="s">
         <v>793</v>
       </c>
-      <c r="B15" s="1" t="s">
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="13" t="s">
+        <v>777</v>
+      </c>
+      <c r="B16" s="13" t="s">
         <v>794</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
-        <v>776</v>
-      </c>
-      <c r="B16" s="1" t="s">
+    <row r="17" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="13" t="s">
         <v>795</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
+      <c r="B17" s="13" t="s">
         <v>796</v>
       </c>
-      <c r="B17" s="1" t="s">
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="12" t="s">
+        <v>785</v>
+      </c>
+      <c r="B18" s="12" t="s">
         <v>797</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
-        <v>784</v>
-      </c>
-      <c r="B18" s="1" t="s">
+    <row r="20" spans="1:2" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A20" s="20"/>
+      <c r="B20" s="21" t="s">
         <v>798</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
+    <row r="21" spans="1:2" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A21" s="14"/>
+      <c r="B21" s="12" t="s">
         <v>799</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
-        <v>801</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>802</v>
       </c>
     </row>
   </sheetData>
@@ -7386,161 +7493,162 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB231983-C483-4880-BF8F-1DAE69FC51E8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF5A5382-D22C-4A37-A263-EBF3B832721F}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.77734375" customWidth="1"/>
-    <col min="2" max="2" width="45.77734375" customWidth="1"/>
-    <col min="3" max="3" width="55.77734375" customWidth="1"/>
+    <col min="1" max="1" width="26.77734375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="48.77734375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="58.77734375" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="11.5546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="16" t="s">
+        <v>800</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="18" t="s">
+        <v>801</v>
+      </c>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="11" t="s">
+        <v>802</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>803</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-    </row>
-    <row r="2" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="C4" s="11" t="s">
         <v>804</v>
       </c>
-      <c r="B2" s="1" t="s">
+    </row>
+    <row r="5" spans="1:3" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="15" t="s">
         <v>805</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
+      <c r="B5" s="13" t="s">
         <v>806</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="C5" s="13" t="s">
         <v>807</v>
       </c>
-      <c r="C4" s="6" t="s">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="15" t="s">
         <v>808</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="B6" s="13" t="s">
         <v>809</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C6" s="13" t="s">
         <v>810</v>
       </c>
-      <c r="C5" s="1" t="s">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="15" t="s">
         <v>811</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="B7" s="13" t="s">
         <v>812</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C7" s="13" t="s">
         <v>813</v>
       </c>
-      <c r="C6" s="1" t="s">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="15" t="s">
         <v>814</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+      <c r="B8" s="13" t="s">
         <v>815</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C8" s="13" t="s">
         <v>816</v>
       </c>
-      <c r="C7" s="1" t="s">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="15" t="s">
         <v>817</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+      <c r="B9" s="13" t="s">
         <v>818</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C9" s="13" t="s">
         <v>819</v>
       </c>
-      <c r="C8" s="1" t="s">
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="15" t="s">
         <v>820</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+      <c r="B10" s="13" t="s">
         <v>821</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C10" s="13" t="s">
         <v>822</v>
       </c>
-      <c r="C9" s="1" t="s">
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="15" t="s">
         <v>823</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+      <c r="B11" s="13" t="s">
         <v>824</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C11" s="13" t="s">
         <v>825</v>
       </c>
-      <c r="C10" s="1" t="s">
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="15" t="s">
         <v>826</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+      <c r="B12" s="13" t="s">
         <v>827</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="C12" s="13" t="s">
         <v>828</v>
       </c>
-      <c r="C11" s="1" t="s">
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="15" t="s">
         <v>829</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+      <c r="B13" s="13" t="s">
         <v>830</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="C13" s="13" t="s">
         <v>831</v>
       </c>
-      <c r="C12" s="1" t="s">
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="14" t="s">
         <v>832</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
+      <c r="B14" s="12" t="s">
         <v>833</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="C14" s="12" t="s">
         <v>834</v>
       </c>
-      <c r="C13" s="1" t="s">
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="18" t="s">
         <v>835</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>836</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>837</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
-        <v>839</v>
-      </c>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
     <mergeCell ref="A16:C16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7548,130 +7656,131 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA9DD675-0ED8-446E-9420-841FCD9A084F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8B4D14D-9766-4184-915E-E4ACD26FBAA5}">
   <dimension ref="A1:B15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.77734375" customWidth="1"/>
-    <col min="2" max="2" width="70.77734375" customWidth="1"/>
+    <col min="1" max="1" width="32.77734375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="75.77734375" style="1" customWidth="1"/>
+    <col min="3" max="16384" width="11.5546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="16" t="s">
+        <v>836</v>
+      </c>
+      <c r="B1" s="16"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="11" t="s">
+        <v>837</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="15" t="s">
+        <v>839</v>
+      </c>
+      <c r="B3" s="13" t="s">
         <v>840</v>
       </c>
-      <c r="B1" s="7"/>
-    </row>
-    <row r="2" spans="1:2" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="15" t="s">
         <v>841</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B4" s="13" t="s">
         <v>842</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="15" t="s">
         <v>843</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B5" s="13" t="s">
         <v>844</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="15" t="s">
         <v>845</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B6" s="13" t="s">
         <v>846</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="15" t="s">
         <v>847</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B7" s="13" t="s">
         <v>848</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="15" t="s">
+        <v>261</v>
+      </c>
+      <c r="B8" s="13" t="s">
         <v>849</v>
       </c>
-      <c r="B6" s="1" t="s">
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="15" t="s">
         <v>850</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+      <c r="B9" s="13" t="s">
         <v>851</v>
       </c>
-      <c r="B7" s="1" t="s">
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="15" t="s">
         <v>852</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="B8" s="1" t="s">
+      <c r="B10" s="13" t="s">
         <v>853</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="15" t="s">
         <v>854</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B11" s="13" t="s">
         <v>855</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="15" t="s">
         <v>856</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B12" s="13" t="s">
         <v>857</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="15" t="s">
         <v>858</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B13" s="13" t="s">
         <v>859</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="15" t="s">
         <v>860</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B14" s="13" t="s">
         <v>861</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="14" t="s">
         <v>862</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B15" s="12" t="s">
         <v>863</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>864</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>865</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>866</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>867</v>
       </c>
     </row>
   </sheetData>
